--- a/F1 Championship Tracker and Scenario Model.xlsx
+++ b/F1 Championship Tracker and Scenario Model.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/83ee6083a630dad4/Documents/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1295" documentId="8_{75E99248-D14D-4C4F-AB99-B7AADEEB1DE1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EE72A6AD-F256-4138-BF9B-44A539A6B89A}"/>
+  <xr:revisionPtr revIDLastSave="1350" documentId="8_{75E99248-D14D-4C4F-AB99-B7AADEEB1DE1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7132C07C-291C-4287-9E36-FEBA9611D38F}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="2" activeTab="3" xr2:uid="{D3B98087-E543-4FEF-BD88-51BD634FA9D6}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="1" activeTab="1" xr2:uid="{D3B98087-E543-4FEF-BD88-51BD634FA9D6}"/>
   </bookViews>
   <sheets>
     <sheet name="Main Page" sheetId="3" r:id="rId1"/>
@@ -75,7 +75,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="594" uniqueCount="99">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="616" uniqueCount="99">
   <si>
     <t>POS</t>
   </si>
@@ -378,7 +378,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="12" x14ac:knownFonts="1">
+  <fonts count="14" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -472,8 +472,23 @@
       <name val="Agency FB"/>
       <family val="2"/>
     </font>
+    <font>
+      <b/>
+      <sz val="16"/>
+      <color rgb="FFFF0000"/>
+      <name val="Agency FB"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <u/>
+      <sz val="16"/>
+      <color rgb="FFFF0000"/>
+      <name val="Agency FB"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="20">
+  <fills count="23">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -592,6 +607,24 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD4AF37"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA37A1A"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.14999847407452621"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="7">
     <border>
@@ -673,7 +706,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="50">
+  <cellXfs count="61">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -807,13 +840,46 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="15" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="15" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="20" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="21" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="22" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="22" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="19" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="19" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="19" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -840,107 +906,6 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="16"/>
-        <color theme="1"/>
-        <name val="Agency FB"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.79998168889431442"/>
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right/>
-        <top style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </top>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <left style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </left>
-        <right style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </right>
-        <top style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </top>
-        <bottom style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="16"/>
-        <color theme="1"/>
-        <name val="Agency FB"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.79998168889431442"/>
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u/>
-        <vertAlign val="baseline"/>
-        <sz val="16"/>
-        <color theme="0"/>
-        <name val="Agency FB"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -1212,19 +1177,120 @@
       </font>
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="16"/>
+        <color theme="1"/>
+        <name val="Agency FB"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.79998168889431442"/>
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <left style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </left>
+        <right style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </right>
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="16"/>
+        <color theme="1"/>
+        <name val="Agency FB"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.79998168889431442"/>
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u/>
+        <vertAlign val="baseline"/>
+        <sz val="16"/>
+        <color theme="0"/>
+        <name val="Agency FB"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <mruColors>
+      <color rgb="FFA37A1A"/>
+      <color rgb="FF9C9FA2"/>
       <color rgb="FFD4AF37"/>
       <color rgb="FFF3E5AB"/>
-      <color rgb="FFA37A1A"/>
       <color rgb="FF00A1E8"/>
       <color rgb="FF909090"/>
       <color rgb="FF1868DB"/>
       <color rgb="FF6C98FF"/>
       <color rgb="FF4781D7"/>
-      <color rgb="FF9C9FA2"/>
       <color rgb="FFED1131"/>
     </mruColors>
   </colors>
@@ -1482,40 +1548,40 @@
                   <c:v>154</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>154</c:v>
+                  <c:v>160</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>154</c:v>
+                  <c:v>160</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>154</c:v>
+                  <c:v>160</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>154</c:v>
+                  <c:v>160</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>154</c:v>
+                  <c:v>160</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>154</c:v>
+                  <c:v>160</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>154</c:v>
+                  <c:v>160</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>154</c:v>
+                  <c:v>160</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>154</c:v>
+                  <c:v>160</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>154</c:v>
+                  <c:v>160</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>154</c:v>
+                  <c:v>160</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>154</c:v>
+                  <c:v>160</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1688,40 +1754,40 @@
                   <c:v>159</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>159</c:v>
+                  <c:v>169</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>159</c:v>
+                  <c:v>169</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>159</c:v>
+                  <c:v>169</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>159</c:v>
+                  <c:v>169</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>159</c:v>
+                  <c:v>169</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>159</c:v>
+                  <c:v>169</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>159</c:v>
+                  <c:v>169</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>159</c:v>
+                  <c:v>169</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>159</c:v>
+                  <c:v>169</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>159</c:v>
+                  <c:v>169</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>159</c:v>
+                  <c:v>169</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>159</c:v>
+                  <c:v>169</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1894,40 +1960,40 @@
                   <c:v>126</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>126</c:v>
+                  <c:v>138</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>126</c:v>
+                  <c:v>138</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>126</c:v>
+                  <c:v>138</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>126</c:v>
+                  <c:v>138</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>126</c:v>
+                  <c:v>138</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>126</c:v>
+                  <c:v>138</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>126</c:v>
+                  <c:v>138</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>126</c:v>
+                  <c:v>138</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>126</c:v>
+                  <c:v>138</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>126</c:v>
+                  <c:v>138</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>126</c:v>
+                  <c:v>138</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>126</c:v>
+                  <c:v>138</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1948,7 +2014,7 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>Max Verstappen</c:v>
+                  <c:v>Lando Norris</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -2070,76 +2136,76 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="24"/>
                 <c:pt idx="0">
-                  <c:v>8</c:v>
+                  <c:v>10</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>8</c:v>
+                  <c:v>15</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>12</c:v>
+                  <c:v>25</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>12</c:v>
+                  <c:v>25</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>12</c:v>
+                  <c:v>25</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>26</c:v>
+                  <c:v>51</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>43</c:v>
+                  <c:v>58</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>43</c:v>
+                  <c:v>58</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>55</c:v>
+                  <c:v>73</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>73</c:v>
+                  <c:v>79</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>76</c:v>
+                  <c:v>97</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>91</c:v>
+                  <c:v>103</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>91</c:v>
+                  <c:v>128</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>91</c:v>
+                  <c:v>128</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>91</c:v>
+                  <c:v>128</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>91</c:v>
+                  <c:v>128</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>91</c:v>
+                  <c:v>128</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>91</c:v>
+                  <c:v>128</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>91</c:v>
+                  <c:v>128</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>91</c:v>
+                  <c:v>128</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>91</c:v>
+                  <c:v>128</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>91</c:v>
+                  <c:v>128</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>91</c:v>
+                  <c:v>128</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>91</c:v>
+                  <c:v>128</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2318,40 +2384,40 @@
                   <c:v>204</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>204</c:v>
+                  <c:v>219</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>204</c:v>
+                  <c:v>219</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>204</c:v>
+                  <c:v>219</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>204</c:v>
+                  <c:v>219</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>204</c:v>
+                  <c:v>219</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>204</c:v>
+                  <c:v>219</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>204</c:v>
+                  <c:v>219</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>204</c:v>
+                  <c:v>219</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>204</c:v>
+                  <c:v>219</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>204</c:v>
+                  <c:v>219</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>204</c:v>
+                  <c:v>219</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>204</c:v>
+                  <c:v>219</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2809,67 +2875,67 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
+                  <c:v>59</c:v>
+                </c:pt>
+                <c:pt idx="2">
                   <c:v>50</c:v>
                 </c:pt>
-                <c:pt idx="2">
-                  <c:v>45</c:v>
-                </c:pt>
                 <c:pt idx="3">
-                  <c:v>78</c:v>
+                  <c:v>81</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>101</c:v>
+                  <c:v>91</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>112</c:v>
+                  <c:v>127</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>113</c:v>
+                  <c:v>110</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>144</c:v>
+                  <c:v>151</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>162</c:v>
+                  <c:v>177</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>185</c:v>
+                  <c:v>200</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>182</c:v>
+                  <c:v>196</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>165</c:v>
+                  <c:v>176</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>186</c:v>
+                  <c:v>201</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>201</c:v>
+                  <c:v>216</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>204</c:v>
+                  <c:v>217</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>194</c:v>
+                  <c:v>209</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>199</c:v>
+                  <c:v>214</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>198</c:v>
+                  <c:v>213</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>203</c:v>
+                  <c:v>218</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>204</c:v>
+                  <c:v>219</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>204</c:v>
+                  <c:v>219</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>204</c:v>
+                  <c:v>219</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4174,15 +4240,15 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>598712</xdr:colOff>
-      <xdr:row>0</xdr:row>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>4352</xdr:colOff>
+      <xdr:row>1</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>21</xdr:col>
-      <xdr:colOff>10885</xdr:colOff>
-      <xdr:row>27</xdr:row>
+      <xdr:colOff>26125</xdr:colOff>
+      <xdr:row>28</xdr:row>
       <xdr:rowOff>174170</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
@@ -4213,15 +4279,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>21</xdr:col>
-      <xdr:colOff>163285</xdr:colOff>
+      <xdr:colOff>224245</xdr:colOff>
       <xdr:row>0</xdr:row>
-      <xdr:rowOff>10883</xdr:rowOff>
+      <xdr:rowOff>178523</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>34</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>27</xdr:row>
-      <xdr:rowOff>174171</xdr:rowOff>
+      <xdr:colOff>60960</xdr:colOff>
+      <xdr:row>28</xdr:row>
+      <xdr:rowOff>158931</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -4256,14 +4322,14 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{4280D490-D4D3-43A3-A20D-31221A04B60B}" name="Table2" displayName="Table2" ref="D2:F7" totalsRowShown="0" headerRowDxfId="25" dataDxfId="24">
-  <autoFilter ref="D2:F7" xr:uid="{4280D490-D4D3-43A3-A20D-31221A04B60B}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{4280D490-D4D3-43A3-A20D-31221A04B60B}" name="Table2" displayName="Table2" ref="E3:G8" totalsRowShown="0" headerRowDxfId="21" dataDxfId="20">
+  <autoFilter ref="E3:G8" xr:uid="{4280D490-D4D3-43A3-A20D-31221A04B60B}"/>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{E88D70F2-B220-443A-9C88-8BDB3414BE2E}" name="Rank" dataDxfId="23"/>
-    <tableColumn id="2" xr3:uid="{819A3862-68F5-4864-A4DB-D8FEBA20F88B}" name="Team" dataDxfId="22">
+    <tableColumn id="1" xr3:uid="{E88D70F2-B220-443A-9C88-8BDB3414BE2E}" name="Rank" dataDxfId="19"/>
+    <tableColumn id="2" xr3:uid="{819A3862-68F5-4864-A4DB-D8FEBA20F88B}" name="Team" dataDxfId="18">
       <calculatedColumnFormula>'Constructors Standings'!AC2</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{91FD9857-103C-4298-BA33-256B39B65DD9}" name="Points" dataDxfId="21">
+    <tableColumn id="3" xr3:uid="{91FD9857-103C-4298-BA33-256B39B65DD9}" name="Points" dataDxfId="17">
       <calculatedColumnFormula>'Constructors Standings'!AD2</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -4272,14 +4338,14 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{C9F4CE16-89B2-4DA7-82DE-AC1342F239B3}" name="Table3" displayName="Table3" ref="A2:C7" totalsRowShown="0" headerRowDxfId="20" dataDxfId="19">
-  <autoFilter ref="A2:C7" xr:uid="{C9F4CE16-89B2-4DA7-82DE-AC1342F239B3}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{C9F4CE16-89B2-4DA7-82DE-AC1342F239B3}" name="Table3" displayName="Table3" ref="B3:D8" totalsRowShown="0" headerRowDxfId="16" dataDxfId="15">
+  <autoFilter ref="B3:D8" xr:uid="{C9F4CE16-89B2-4DA7-82DE-AC1342F239B3}"/>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{4537E759-109B-4EBD-A344-E255E63C6270}" name="Rank" dataDxfId="18"/>
-    <tableColumn id="2" xr3:uid="{5E4B89B7-E359-4BDB-94E6-F53C078F3BA5}" name="Driver" dataDxfId="17">
+    <tableColumn id="1" xr3:uid="{4537E759-109B-4EBD-A344-E255E63C6270}" name="Rank" dataDxfId="14"/>
+    <tableColumn id="2" xr3:uid="{5E4B89B7-E359-4BDB-94E6-F53C078F3BA5}" name="Driver" dataDxfId="13">
       <calculatedColumnFormula>'Drivers'' Standings'!AE2</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{62B1C38D-704A-41CF-95E9-3BCB8A5241B3}" name="Points" dataDxfId="16">
+    <tableColumn id="3" xr3:uid="{62B1C38D-704A-41CF-95E9-3BCB8A5241B3}" name="Points" dataDxfId="12">
       <calculatedColumnFormula>'Drivers'' Standings'!AF2</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -4288,16 +4354,16 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{70D1B7CF-5273-4AB7-831E-599AF89C2ED8}" name="Table1" displayName="Table1" ref="AD1:AF23" totalsRowShown="0" headerRowDxfId="15" dataDxfId="14">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{70D1B7CF-5273-4AB7-831E-599AF89C2ED8}" name="Table1" displayName="Table1" ref="AD1:AF23" totalsRowShown="0" headerRowDxfId="11" dataDxfId="10">
   <autoFilter ref="AD1:AF23" xr:uid="{70D1B7CF-5273-4AB7-831E-599AF89C2ED8}"/>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{A3E7A5CE-5089-4B54-B6F6-EF0FC064E0A8}" name="RANK" dataDxfId="13">
+    <tableColumn id="1" xr3:uid="{A3E7A5CE-5089-4B54-B6F6-EF0FC064E0A8}" name="RANK" dataDxfId="9">
       <calculatedColumnFormula>ROW()-1</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{AEF03291-BBEF-420B-B63C-52CA498C7574}" name="DRIVER" dataDxfId="12">
+    <tableColumn id="2" xr3:uid="{AEF03291-BBEF-420B-B63C-52CA498C7574}" name="DRIVER" dataDxfId="8">
       <calculatedColumnFormula>INDEX($B$2:$B$23,MATCH(AD2,$AA$2:$AA$23,0))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{F47480B5-F91D-474C-8CCB-A603161AC8A5}" name="POINTS" dataDxfId="11">
+    <tableColumn id="3" xr3:uid="{F47480B5-F91D-474C-8CCB-A603161AC8A5}" name="POINTS" dataDxfId="7">
       <calculatedColumnFormula>INDEX($AB$2:$AB$23,MATCH(AD2,$AA$2:$AA$23,0))</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -4306,10 +4372,10 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{75B324FA-8D76-45F8-AF65-C229EA767CC7}" name="Table7" displayName="Table7" ref="Z1:Z12" totalsRowShown="0" headerRowDxfId="10" dataDxfId="9" tableBorderDxfId="8">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{75B324FA-8D76-45F8-AF65-C229EA767CC7}" name="Table7" displayName="Table7" ref="Z1:Z12" totalsRowShown="0" headerRowDxfId="25" dataDxfId="24" tableBorderDxfId="23">
   <autoFilter ref="Z1:Z12" xr:uid="{75B324FA-8D76-45F8-AF65-C229EA767CC7}"/>
   <tableColumns count="1">
-    <tableColumn id="1" xr3:uid="{44EB4C70-286C-4A21-A881-4C84C5B3BD28}" name="POINTS" dataDxfId="7">
+    <tableColumn id="1" xr3:uid="{44EB4C70-286C-4A21-A881-4C84C5B3BD28}" name="POINTS" dataDxfId="22">
       <calculatedColumnFormula>SUM(B2:Y2)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -4659,169 +4725,170 @@
   <sheetPr>
     <tabColor rgb="FF002060"/>
   </sheetPr>
-  <dimension ref="A1:G11"/>
+  <dimension ref="B2:G11"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="6" width="16.77734375" customWidth="1"/>
+    <col min="1" max="1" width="8.88671875" customWidth="1"/>
+    <col min="2" max="6" width="16.77734375" customWidth="1"/>
     <col min="7" max="7" width="8.88671875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="22.2" x14ac:dyDescent="0.3">
-      <c r="A1" s="47" t="s">
+    <row r="2" spans="2:7" ht="22.2" x14ac:dyDescent="0.3">
+      <c r="B2" s="58" t="s">
         <v>96</v>
       </c>
-      <c r="B1" s="47"/>
-      <c r="C1" s="47"/>
-      <c r="D1" s="47"/>
-      <c r="E1" s="47"/>
-      <c r="F1" s="47"/>
+      <c r="C2" s="58"/>
+      <c r="D2" s="58"/>
+      <c r="E2" s="58"/>
+      <c r="F2" s="58"/>
+      <c r="G2" s="58"/>
     </row>
-    <row r="2" spans="1:7" ht="22.2" x14ac:dyDescent="0.35">
-      <c r="A2" s="45" t="s">
+    <row r="3" spans="2:7" ht="22.2" x14ac:dyDescent="0.35">
+      <c r="B3" s="45" t="s">
         <v>95</v>
       </c>
-      <c r="B2" s="45" t="s">
+      <c r="C3" s="45" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="45" t="s">
+      <c r="D3" s="45" t="s">
         <v>3</v>
       </c>
-      <c r="D2" s="45" t="s">
+      <c r="E3" s="45" t="s">
         <v>95</v>
       </c>
-      <c r="E2" s="45" t="s">
+      <c r="F3" s="45" t="s">
         <v>2</v>
       </c>
-      <c r="F2" s="45" t="s">
+      <c r="G3" s="45" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="22.2" x14ac:dyDescent="0.35">
-      <c r="A3" s="45">
+    <row r="4" spans="2:7" ht="22.2" x14ac:dyDescent="0.35">
+      <c r="B4" s="45">
         <v>1</v>
       </c>
-      <c r="B3" s="45" t="str">
+      <c r="C4" s="45" t="str">
         <f>'Drivers'' Standings'!AE2</f>
         <v>ANT</v>
       </c>
-      <c r="C3" s="45">
+      <c r="D4" s="45">
         <f>'Drivers'' Standings'!AF2</f>
-        <v>204</v>
-      </c>
-      <c r="D3" s="45">
+        <v>219</v>
+      </c>
+      <c r="E4" s="45">
         <v>1</v>
       </c>
-      <c r="E3" s="45" t="str">
+      <c r="F4" s="45" t="str">
         <f>'Constructors Standings'!AC2</f>
         <v>Mercedes</v>
       </c>
-      <c r="F3" s="45">
+      <c r="G4" s="45">
         <f>'Constructors Standings'!AD2</f>
-        <v>358</v>
+        <v>379</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="22.2" x14ac:dyDescent="0.35">
-      <c r="A4" s="45">
+    <row r="5" spans="2:7" ht="22.2" x14ac:dyDescent="0.35">
+      <c r="B5" s="45">
         <v>2</v>
       </c>
-      <c r="B4" s="45" t="str">
+      <c r="C5" s="45" t="str">
         <f>'Drivers'' Standings'!AE3</f>
         <v>HAM</v>
       </c>
-      <c r="C4" s="45">
+      <c r="D5" s="45">
         <f>'Drivers'' Standings'!AF3</f>
-        <v>159</v>
-      </c>
-      <c r="D4" s="45">
+        <v>169</v>
+      </c>
+      <c r="E5" s="45">
         <v>2</v>
       </c>
-      <c r="E4" s="45" t="str">
+      <c r="F5" s="45" t="str">
         <f>'Constructors Standings'!AC3</f>
         <v>Ferrari</v>
       </c>
-      <c r="F4" s="45">
+      <c r="G5" s="45">
         <f>'Constructors Standings'!AD3</f>
-        <v>285</v>
+        <v>307</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="22.2" x14ac:dyDescent="0.35">
-      <c r="A5" s="45">
+    <row r="6" spans="2:7" ht="22.2" x14ac:dyDescent="0.35">
+      <c r="B6" s="45">
         <v>3</v>
       </c>
-      <c r="B5" s="45" t="str">
+      <c r="C6" s="45" t="str">
         <f>'Drivers'' Standings'!AE4</f>
         <v>RUS</v>
       </c>
-      <c r="C5" s="45">
+      <c r="D6" s="45">
         <f>'Drivers'' Standings'!AF4</f>
-        <v>154</v>
-      </c>
-      <c r="D5" s="45">
+        <v>160</v>
+      </c>
+      <c r="E6" s="45">
         <v>3</v>
       </c>
-      <c r="E5" s="45" t="str">
+      <c r="F6" s="45" t="str">
         <f>'Constructors Standings'!AC4</f>
         <v>McLaren</v>
       </c>
-      <c r="F5" s="45">
+      <c r="G6" s="45">
         <f>'Constructors Standings'!AD4</f>
-        <v>195</v>
+        <v>220</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="22.2" x14ac:dyDescent="0.35">
-      <c r="A6" s="45">
+    <row r="7" spans="2:7" ht="22.2" x14ac:dyDescent="0.35">
+      <c r="B7" s="45">
         <v>4</v>
       </c>
-      <c r="B6" s="45" t="str">
+      <c r="C7" s="45" t="str">
         <f>'Drivers'' Standings'!AE5</f>
         <v>LEC</v>
       </c>
-      <c r="C6" s="45">
+      <c r="D7" s="45">
         <f>'Drivers'' Standings'!AF5</f>
-        <v>126</v>
-      </c>
-      <c r="D6" s="45">
+        <v>138</v>
+      </c>
+      <c r="E7" s="45">
         <v>4</v>
       </c>
-      <c r="E6" s="45" t="str">
+      <c r="F7" s="45" t="str">
         <f>'Constructors Standings'!AC5</f>
         <v>Red Bull Racing</v>
       </c>
-      <c r="F6" s="45">
+      <c r="G7" s="45">
         <f>'Constructors Standings'!AD5</f>
-        <v>151</v>
+        <v>177</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="22.2" x14ac:dyDescent="0.35">
-      <c r="A7" s="45">
+    <row r="8" spans="2:7" ht="22.2" x14ac:dyDescent="0.35">
+      <c r="B8" s="45">
         <v>5</v>
       </c>
-      <c r="B7" s="45" t="str">
+      <c r="C8" s="45" t="str">
         <f>'Drivers'' Standings'!AE6</f>
         <v>NOR</v>
       </c>
-      <c r="C7" s="45">
+      <c r="D8" s="45">
         <f>'Drivers'' Standings'!AF6</f>
-        <v>103</v>
-      </c>
-      <c r="D7" s="45">
+        <v>128</v>
+      </c>
+      <c r="E8" s="45">
         <v>5</v>
       </c>
-      <c r="E7" s="45" t="str">
+      <c r="F8" s="45" t="str">
         <f>'Constructors Standings'!AC6</f>
-        <v>Alpine</v>
-      </c>
-      <c r="F7" s="45">
+        <v>Racing Bulls</v>
+      </c>
+      <c r="G8" s="45">
         <f>'Constructors Standings'!AD6</f>
-        <v>61</v>
+        <v>66</v>
       </c>
     </row>
-    <row r="11" spans="1:7" ht="22.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="2:7" ht="22.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="G11" s="46"/>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="B2:G2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
@@ -4859,10 +4926,10 @@
       <c r="E1" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="48" t="s">
         <v>19</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="G1" s="48" t="s">
         <v>20</v>
       </c>
       <c r="H1" s="41" t="s">
@@ -4960,11 +5027,11 @@
         <f>IFERROR(VLOOKUP(MATCH($B2,INDEX('Race Resuts'!$A$2:$W$23,0,MATCH(E$1,'Race Resuts'!$A$1:$W$1,0)),0),'Points Refrence'!$A$2:$B$11,2,FALSE),0)</f>
         <v>25</v>
       </c>
-      <c r="F2" s="4">
+      <c r="F2" s="47">
         <f>IFERROR(VLOOKUP(MATCH($B2,INDEX('Race Resuts'!$A$2:$W$23,0,MATCH(F$1,'Race Resuts'!$A$1:$W$1,0)),0),'Points Refrence'!$A$2:$B$11,2,FALSE),0)</f>
         <v>0</v>
       </c>
-      <c r="G2" s="4">
+      <c r="G2" s="47">
         <f>IFERROR(VLOOKUP(MATCH($B2,INDEX('Race Resuts'!$A$2:$W$23,0,MATCH(G$1,'Race Resuts'!$A$1:$W$1,0)),0),'Points Refrence'!$A$2:$B$11,2,FALSE),0)</f>
         <v>0</v>
       </c>
@@ -4998,7 +5065,7 @@
       </c>
       <c r="O2" s="4">
         <f>IFERROR(VLOOKUP(MATCH($B2,INDEX('Race Resuts'!$A$2:$W$23,0,MATCH(O$1,'Race Resuts'!$A$1:$W$1,0)),0),'Points Refrence'!$A$2:$B$11,2,FALSE),0)</f>
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="P2" s="42">
         <f>IFERROR(VLOOKUP(MATCH($B2,INDEX('Race Resuts'!$B$2:$W$23,0,MATCH(P$1,'Race Resuts'!$B$1:$W$1,0)),0),'Points Refrence'!$A$2:$B$11,2,FALSE),0)+IFERROR(VLOOKUP(MATCH($B2,INDEX('Sprint Race Results'!$B$2:$G$23,0,MATCH(P$1,'Sprint Race Results'!$B$1:$G$1,0)),0),'Points Refrence'!$D$2:$E$9,2,FALSE),0)</f>
@@ -5050,7 +5117,7 @@
       </c>
       <c r="AB2" s="7">
         <f>SUM(C2:Z2)</f>
-        <v>204</v>
+        <v>219</v>
       </c>
       <c r="AD2" s="4">
         <f>ROW()-1</f>
@@ -5062,7 +5129,7 @@
       </c>
       <c r="AF2" s="4">
         <f>INDEX($AB$2:$AB$23,MATCH(AD2,$AA$2:$AA$23,0))</f>
-        <v>204</v>
+        <v>219</v>
       </c>
       <c r="AH2" s="43" t="str">
         <f>AE$2</f>
@@ -5088,11 +5155,11 @@
         <f>IFERROR(VLOOKUP(MATCH($B3,INDEX('Race Resuts'!$A$2:$W$23,0,MATCH(E$1,'Race Resuts'!$A$1:$W$1,0)),0),'Points Refrence'!$A$2:$B$11,2,FALSE),0)</f>
         <v>12</v>
       </c>
-      <c r="F3" s="4">
+      <c r="F3" s="47">
         <f>IFERROR(VLOOKUP(MATCH($B3,INDEX('Race Resuts'!$A$2:$W$23,0,MATCH(F$1,'Race Resuts'!$A$1:$W$1,0)),0),'Points Refrence'!$A$2:$B$11,2,FALSE),0)</f>
         <v>0</v>
       </c>
-      <c r="G3" s="4">
+      <c r="G3" s="47">
         <f>IFERROR(VLOOKUP(MATCH($B3,INDEX('Race Resuts'!$A$2:$W$23,0,MATCH(G$1,'Race Resuts'!$A$1:$W$1,0)),0),'Points Refrence'!$A$2:$B$11,2,FALSE),0)</f>
         <v>0</v>
       </c>
@@ -5126,7 +5193,7 @@
       </c>
       <c r="O3" s="4">
         <f>IFERROR(VLOOKUP(MATCH($B3,INDEX('Race Resuts'!$A$2:$W$23,0,MATCH(O$1,'Race Resuts'!$A$1:$W$1,0)),0),'Points Refrence'!$A$2:$B$11,2,FALSE),0)</f>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="P3" s="42">
         <f>IFERROR(VLOOKUP(MATCH($B3,INDEX('Race Resuts'!$B$2:$W$23,0,MATCH(P$1,'Race Resuts'!$B$1:$W$1,0)),0),'Points Refrence'!$A$2:$B$11,2,FALSE),0)+IFERROR(VLOOKUP(MATCH($B3,INDEX('Sprint Race Results'!$B$2:$G$23,0,MATCH(P$1,'Sprint Race Results'!$B$1:$G$1,0)),0),'Points Refrence'!$D$2:$E$9,2,FALSE),0)</f>
@@ -5178,7 +5245,7 @@
       </c>
       <c r="AB3" s="7">
         <f t="shared" ref="AB3:AB23" si="0">SUM(C3:Z3)</f>
-        <v>154</v>
+        <v>160</v>
       </c>
       <c r="AD3" s="4">
         <f t="shared" ref="AD3:AD23" si="1">ROW()-1</f>
@@ -5190,7 +5257,7 @@
       </c>
       <c r="AF3" s="4">
         <f t="shared" ref="AF3:AF23" si="3">INDEX($AB$2:$AB$23,MATCH(AD3,$AA$2:$AA$23,0))</f>
-        <v>159</v>
+        <v>169</v>
       </c>
     </row>
     <row r="4" spans="1:34" ht="21.6" x14ac:dyDescent="0.4">
@@ -5212,11 +5279,11 @@
         <f>IFERROR(VLOOKUP(MATCH($B4,INDEX('Race Resuts'!$A$2:$W$23,0,MATCH(E$1,'Race Resuts'!$A$1:$W$1,0)),0),'Points Refrence'!$A$2:$B$11,2,FALSE),0)</f>
         <v>8</v>
       </c>
-      <c r="F4" s="4">
+      <c r="F4" s="47">
         <f>IFERROR(VLOOKUP(MATCH($B4,INDEX('Race Resuts'!$A$2:$W$23,0,MATCH(F$1,'Race Resuts'!$A$1:$W$1,0)),0),'Points Refrence'!$A$2:$B$11,2,FALSE),0)</f>
         <v>0</v>
       </c>
-      <c r="G4" s="4">
+      <c r="G4" s="47">
         <f>IFERROR(VLOOKUP(MATCH($B4,INDEX('Race Resuts'!$A$2:$W$23,0,MATCH(G$1,'Race Resuts'!$A$1:$W$1,0)),0),'Points Refrence'!$A$2:$B$11,2,FALSE),0)</f>
         <v>0</v>
       </c>
@@ -5250,7 +5317,7 @@
       </c>
       <c r="O4" s="4">
         <f>IFERROR(VLOOKUP(MATCH($B4,INDEX('Race Resuts'!$A$2:$W$23,0,MATCH(O$1,'Race Resuts'!$A$1:$W$1,0)),0),'Points Refrence'!$A$2:$B$11,2,FALSE),0)</f>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="P4" s="42">
         <f>IFERROR(VLOOKUP(MATCH($B4,INDEX('Race Resuts'!$B$2:$W$23,0,MATCH(P$1,'Race Resuts'!$B$1:$W$1,0)),0),'Points Refrence'!$A$2:$B$11,2,FALSE),0)+IFERROR(VLOOKUP(MATCH($B4,INDEX('Sprint Race Results'!$B$2:$G$23,0,MATCH(P$1,'Sprint Race Results'!$B$1:$G$1,0)),0),'Points Refrence'!$D$2:$E$9,2,FALSE),0)</f>
@@ -5302,7 +5369,7 @@
       </c>
       <c r="AB4" s="7">
         <f t="shared" si="0"/>
-        <v>159</v>
+        <v>169</v>
       </c>
       <c r="AD4" s="4">
         <f t="shared" si="1"/>
@@ -5314,7 +5381,7 @@
       </c>
       <c r="AF4" s="4">
         <f t="shared" si="3"/>
-        <v>154</v>
+        <v>160</v>
       </c>
     </row>
     <row r="5" spans="1:34" ht="21.6" x14ac:dyDescent="0.4">
@@ -5336,11 +5403,11 @@
         <f>IFERROR(VLOOKUP(MATCH($B5,INDEX('Race Resuts'!$A$2:$W$23,0,MATCH(E$1,'Race Resuts'!$A$1:$W$1,0)),0),'Points Refrence'!$A$2:$B$11,2,FALSE),0)</f>
         <v>15</v>
       </c>
-      <c r="F5" s="4">
+      <c r="F5" s="47">
         <f>IFERROR(VLOOKUP(MATCH($B5,INDEX('Race Resuts'!$A$2:$W$23,0,MATCH(F$1,'Race Resuts'!$A$1:$W$1,0)),0),'Points Refrence'!$A$2:$B$11,2,FALSE),0)</f>
         <v>0</v>
       </c>
-      <c r="G5" s="4">
+      <c r="G5" s="47">
         <f>IFERROR(VLOOKUP(MATCH($B5,INDEX('Race Resuts'!$A$2:$W$23,0,MATCH(G$1,'Race Resuts'!$A$1:$W$1,0)),0),'Points Refrence'!$A$2:$B$11,2,FALSE),0)</f>
         <v>0</v>
       </c>
@@ -5374,7 +5441,7 @@
       </c>
       <c r="O5" s="4">
         <f>IFERROR(VLOOKUP(MATCH($B5,INDEX('Race Resuts'!$A$2:$W$23,0,MATCH(O$1,'Race Resuts'!$A$1:$W$1,0)),0),'Points Refrence'!$A$2:$B$11,2,FALSE),0)</f>
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="P5" s="42">
         <f>IFERROR(VLOOKUP(MATCH($B5,INDEX('Race Resuts'!$B$2:$W$23,0,MATCH(P$1,'Race Resuts'!$B$1:$W$1,0)),0),'Points Refrence'!$A$2:$B$11,2,FALSE),0)+IFERROR(VLOOKUP(MATCH($B5,INDEX('Sprint Race Results'!$B$2:$G$23,0,MATCH(P$1,'Sprint Race Results'!$B$1:$G$1,0)),0),'Points Refrence'!$D$2:$E$9,2,FALSE),0)</f>
@@ -5426,7 +5493,7 @@
       </c>
       <c r="AB5" s="7">
         <f t="shared" si="0"/>
-        <v>126</v>
+        <v>138</v>
       </c>
       <c r="AD5" s="4">
         <f t="shared" si="1"/>
@@ -5438,7 +5505,7 @@
       </c>
       <c r="AF5" s="4">
         <f t="shared" si="3"/>
-        <v>126</v>
+        <v>138</v>
       </c>
     </row>
     <row r="6" spans="1:34" ht="21.6" x14ac:dyDescent="0.4">
@@ -5460,11 +5527,11 @@
         <f>IFERROR(VLOOKUP(MATCH($B6,INDEX('Race Resuts'!$A$2:$W$23,0,MATCH(E$1,'Race Resuts'!$A$1:$W$1,0)),0),'Points Refrence'!$A$2:$B$11,2,FALSE),0)</f>
         <v>10</v>
       </c>
-      <c r="F6" s="4">
+      <c r="F6" s="47">
         <f>IFERROR(VLOOKUP(MATCH($B6,INDEX('Race Resuts'!$A$2:$W$23,0,MATCH(F$1,'Race Resuts'!$A$1:$W$1,0)),0),'Points Refrence'!$A$2:$B$11,2,FALSE),0)</f>
         <v>0</v>
       </c>
-      <c r="G6" s="4">
+      <c r="G6" s="47">
         <f>IFERROR(VLOOKUP(MATCH($B6,INDEX('Race Resuts'!$A$2:$W$23,0,MATCH(G$1,'Race Resuts'!$A$1:$W$1,0)),0),'Points Refrence'!$A$2:$B$11,2,FALSE),0)</f>
         <v>0</v>
       </c>
@@ -5498,7 +5565,7 @@
       </c>
       <c r="O6" s="4">
         <f>IFERROR(VLOOKUP(MATCH($B6,INDEX('Race Resuts'!$A$2:$W$23,0,MATCH(O$1,'Race Resuts'!$A$1:$W$1,0)),0),'Points Refrence'!$A$2:$B$11,2,FALSE),0)</f>
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="P6" s="42">
         <f>IFERROR(VLOOKUP(MATCH($B6,INDEX('Race Resuts'!$B$2:$W$23,0,MATCH(P$1,'Race Resuts'!$B$1:$W$1,0)),0),'Points Refrence'!$A$2:$B$11,2,FALSE),0)+IFERROR(VLOOKUP(MATCH($B6,INDEX('Sprint Race Results'!$B$2:$G$23,0,MATCH(P$1,'Sprint Race Results'!$B$1:$G$1,0)),0),'Points Refrence'!$D$2:$E$9,2,FALSE),0)</f>
@@ -5550,7 +5617,7 @@
       </c>
       <c r="AB6" s="7">
         <f t="shared" si="0"/>
-        <v>103</v>
+        <v>128</v>
       </c>
       <c r="AD6" s="4">
         <f t="shared" si="1"/>
@@ -5562,7 +5629,7 @@
       </c>
       <c r="AF6" s="4">
         <f t="shared" si="3"/>
-        <v>103</v>
+        <v>128</v>
       </c>
     </row>
     <row r="7" spans="1:34" ht="21.6" x14ac:dyDescent="0.4">
@@ -5584,11 +5651,11 @@
         <f>IFERROR(VLOOKUP(MATCH($B7,INDEX('Race Resuts'!$A$2:$W$23,0,MATCH(E$1,'Race Resuts'!$A$1:$W$1,0)),0),'Points Refrence'!$A$2:$B$11,2,FALSE),0)</f>
         <v>18</v>
       </c>
-      <c r="F7" s="4">
+      <c r="F7" s="47">
         <f>IFERROR(VLOOKUP(MATCH($B7,INDEX('Race Resuts'!$A$2:$W$23,0,MATCH(F$1,'Race Resuts'!$A$1:$W$1,0)),0),'Points Refrence'!$A$2:$B$11,2,FALSE),0)</f>
         <v>0</v>
       </c>
-      <c r="G7" s="4">
+      <c r="G7" s="47">
         <f>IFERROR(VLOOKUP(MATCH($B7,INDEX('Race Resuts'!$A$2:$W$23,0,MATCH(G$1,'Race Resuts'!$A$1:$W$1,0)),0),'Points Refrence'!$A$2:$B$11,2,FALSE),0)</f>
         <v>0</v>
       </c>
@@ -5670,7 +5737,7 @@
       </c>
       <c r="AA7" s="7">
         <f>RANK(AB7,$AB$2:$AB$23,0)+COUNTIF($AB$2:AB7,AB7)-1</f>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AB7" s="7">
         <f t="shared" si="0"/>
@@ -5682,11 +5749,11 @@
       </c>
       <c r="AE7" s="4" t="str">
         <f t="shared" si="2"/>
-        <v>PIA</v>
+        <v>VER</v>
       </c>
       <c r="AF7" s="4">
         <f t="shared" si="3"/>
-        <v>92</v>
+        <v>109</v>
       </c>
     </row>
     <row r="8" spans="1:34" ht="21.6" x14ac:dyDescent="0.4">
@@ -5708,11 +5775,11 @@
         <f>IFERROR(VLOOKUP(MATCH($B8,INDEX('Race Resuts'!$A$2:$W$23,0,MATCH(E$1,'Race Resuts'!$A$1:$W$1,0)),0),'Points Refrence'!$A$2:$B$11,2,FALSE),0)</f>
         <v>4</v>
       </c>
-      <c r="F8" s="4">
+      <c r="F8" s="47">
         <f>IFERROR(VLOOKUP(MATCH($B8,INDEX('Race Resuts'!$A$2:$W$23,0,MATCH(F$1,'Race Resuts'!$A$1:$W$1,0)),0),'Points Refrence'!$A$2:$B$11,2,FALSE),0)</f>
         <v>0</v>
       </c>
-      <c r="G8" s="4">
+      <c r="G8" s="47">
         <f>IFERROR(VLOOKUP(MATCH($B8,INDEX('Race Resuts'!$A$2:$W$23,0,MATCH(G$1,'Race Resuts'!$A$1:$W$1,0)),0),'Points Refrence'!$A$2:$B$11,2,FALSE),0)</f>
         <v>0</v>
       </c>
@@ -5746,7 +5813,7 @@
       </c>
       <c r="O8" s="4">
         <f>IFERROR(VLOOKUP(MATCH($B8,INDEX('Race Resuts'!$A$2:$W$23,0,MATCH(O$1,'Race Resuts'!$A$1:$W$1,0)),0),'Points Refrence'!$A$2:$B$11,2,FALSE),0)</f>
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="P8" s="42">
         <f>IFERROR(VLOOKUP(MATCH($B8,INDEX('Race Resuts'!$B$2:$W$23,0,MATCH(P$1,'Race Resuts'!$B$1:$W$1,0)),0),'Points Refrence'!$A$2:$B$11,2,FALSE),0)+IFERROR(VLOOKUP(MATCH($B8,INDEX('Sprint Race Results'!$B$2:$G$23,0,MATCH(P$1,'Sprint Race Results'!$B$1:$G$1,0)),0),'Points Refrence'!$D$2:$E$9,2,FALSE),0)</f>
@@ -5794,11 +5861,11 @@
       </c>
       <c r="AA8" s="7">
         <f>RANK(AB8,$AB$2:$AB$23,0)+COUNTIF($AB$2:AB8,AB8)-1</f>
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AB8" s="7">
         <f t="shared" si="0"/>
-        <v>91</v>
+        <v>109</v>
       </c>
       <c r="AD8" s="4">
         <f t="shared" si="1"/>
@@ -5806,11 +5873,11 @@
       </c>
       <c r="AE8" s="4" t="str">
         <f t="shared" si="2"/>
-        <v>VER</v>
+        <v>PIA</v>
       </c>
       <c r="AF8" s="4">
         <f t="shared" si="3"/>
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="9" spans="1:34" ht="21.6" x14ac:dyDescent="0.4">
@@ -5832,11 +5899,11 @@
         <f>IFERROR(VLOOKUP(MATCH($B9,INDEX('Race Resuts'!$A$2:$W$23,0,MATCH(E$1,'Race Resuts'!$A$1:$W$1,0)),0),'Points Refrence'!$A$2:$B$11,2,FALSE),0)</f>
         <v>0</v>
       </c>
-      <c r="F9" s="4">
+      <c r="F9" s="47">
         <f>IFERROR(VLOOKUP(MATCH($B9,INDEX('Race Resuts'!$A$2:$W$23,0,MATCH(F$1,'Race Resuts'!$A$1:$W$1,0)),0),'Points Refrence'!$A$2:$B$11,2,FALSE),0)</f>
         <v>0</v>
       </c>
-      <c r="G9" s="4">
+      <c r="G9" s="47">
         <f>IFERROR(VLOOKUP(MATCH($B9,INDEX('Race Resuts'!$A$2:$W$23,0,MATCH(G$1,'Race Resuts'!$A$1:$W$1,0)),0),'Points Refrence'!$A$2:$B$11,2,FALSE),0)</f>
         <v>0</v>
       </c>
@@ -5870,7 +5937,7 @@
       </c>
       <c r="O9" s="4">
         <f>IFERROR(VLOOKUP(MATCH($B9,INDEX('Race Resuts'!$A$2:$W$23,0,MATCH(O$1,'Race Resuts'!$A$1:$W$1,0)),0),'Points Refrence'!$A$2:$B$11,2,FALSE),0)</f>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="P9" s="42">
         <f>IFERROR(VLOOKUP(MATCH($B9,INDEX('Race Resuts'!$B$2:$W$23,0,MATCH(P$1,'Race Resuts'!$B$1:$W$1,0)),0),'Points Refrence'!$A$2:$B$11,2,FALSE),0)+IFERROR(VLOOKUP(MATCH($B9,INDEX('Sprint Race Results'!$B$2:$G$23,0,MATCH(P$1,'Sprint Race Results'!$B$1:$G$1,0)),0),'Points Refrence'!$D$2:$E$9,2,FALSE),0)</f>
@@ -5922,7 +5989,7 @@
       </c>
       <c r="AB9" s="7">
         <f t="shared" si="0"/>
-        <v>60</v>
+        <v>68</v>
       </c>
       <c r="AD9" s="4">
         <f t="shared" si="1"/>
@@ -5934,7 +6001,7 @@
       </c>
       <c r="AF9" s="4">
         <f t="shared" si="3"/>
-        <v>60</v>
+        <v>68</v>
       </c>
     </row>
     <row r="10" spans="1:34" ht="21.6" x14ac:dyDescent="0.4">
@@ -5956,11 +6023,11 @@
         <f>IFERROR(VLOOKUP(MATCH($B10,INDEX('Race Resuts'!$A$2:$W$23,0,MATCH(E$1,'Race Resuts'!$A$1:$W$1,0)),0),'Points Refrence'!$A$2:$B$11,2,FALSE),0)</f>
         <v>6</v>
       </c>
-      <c r="F10" s="4">
+      <c r="F10" s="47">
         <f>IFERROR(VLOOKUP(MATCH($B10,INDEX('Race Resuts'!$A$2:$W$23,0,MATCH(F$1,'Race Resuts'!$A$1:$W$1,0)),0),'Points Refrence'!$A$2:$B$11,2,FALSE),0)</f>
         <v>0</v>
       </c>
-      <c r="G10" s="4">
+      <c r="G10" s="47">
         <f>IFERROR(VLOOKUP(MATCH($B10,INDEX('Race Resuts'!$A$2:$W$23,0,MATCH(G$1,'Race Resuts'!$A$1:$W$1,0)),0),'Points Refrence'!$A$2:$B$11,2,FALSE),0)</f>
         <v>0</v>
       </c>
@@ -6042,7 +6109,7 @@
       </c>
       <c r="AA10" s="7">
         <f>RANK(AB10,$AB$2:$AB$23,0)+COUNTIF($AB$2:AB10,AB10)-1</f>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AB10" s="7">
         <f t="shared" si="0"/>
@@ -6054,11 +6121,11 @@
       </c>
       <c r="AE10" s="4" t="str">
         <f t="shared" si="2"/>
-        <v>GAS</v>
+        <v>LAW</v>
       </c>
       <c r="AF10" s="4">
         <f t="shared" si="3"/>
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="11" spans="1:34" ht="21.6" x14ac:dyDescent="0.4">
@@ -6080,11 +6147,11 @@
         <f>IFERROR(VLOOKUP(MATCH($B11,INDEX('Race Resuts'!$A$2:$W$23,0,MATCH(E$1,'Race Resuts'!$A$1:$W$1,0)),0),'Points Refrence'!$A$2:$B$11,2,FALSE),0)</f>
         <v>0</v>
       </c>
-      <c r="F11" s="4">
+      <c r="F11" s="47">
         <f>IFERROR(VLOOKUP(MATCH($B11,INDEX('Race Resuts'!$A$2:$W$23,0,MATCH(F$1,'Race Resuts'!$A$1:$W$1,0)),0),'Points Refrence'!$A$2:$B$11,2,FALSE),0)</f>
         <v>0</v>
       </c>
-      <c r="G11" s="4">
+      <c r="G11" s="47">
         <f>IFERROR(VLOOKUP(MATCH($B11,INDEX('Race Resuts'!$A$2:$W$23,0,MATCH(G$1,'Race Resuts'!$A$1:$W$1,0)),0),'Points Refrence'!$A$2:$B$11,2,FALSE),0)</f>
         <v>0</v>
       </c>
@@ -6178,11 +6245,11 @@
       </c>
       <c r="AE11" s="4" t="str">
         <f t="shared" si="2"/>
-        <v>LAW</v>
+        <v>GAS</v>
       </c>
       <c r="AF11" s="4">
         <f t="shared" si="3"/>
-        <v>39</v>
+        <v>42</v>
       </c>
     </row>
     <row r="12" spans="1:34" ht="21.6" x14ac:dyDescent="0.4">
@@ -6204,11 +6271,11 @@
         <f>IFERROR(VLOOKUP(MATCH($B12,INDEX('Race Resuts'!$A$2:$W$23,0,MATCH(E$1,'Race Resuts'!$A$1:$W$1,0)),0),'Points Refrence'!$A$2:$B$11,2,FALSE),0)</f>
         <v>0</v>
       </c>
-      <c r="F12" s="4">
+      <c r="F12" s="47">
         <f>IFERROR(VLOOKUP(MATCH($B12,INDEX('Race Resuts'!$A$2:$W$23,0,MATCH(F$1,'Race Resuts'!$A$1:$W$1,0)),0),'Points Refrence'!$A$2:$B$11,2,FALSE),0)</f>
         <v>0</v>
       </c>
-      <c r="G12" s="4">
+      <c r="G12" s="47">
         <f>IFERROR(VLOOKUP(MATCH($B12,INDEX('Race Resuts'!$A$2:$W$23,0,MATCH(G$1,'Race Resuts'!$A$1:$W$1,0)),0),'Points Refrence'!$A$2:$B$11,2,FALSE),0)</f>
         <v>0</v>
       </c>
@@ -6242,7 +6309,7 @@
       </c>
       <c r="O12" s="4">
         <f>IFERROR(VLOOKUP(MATCH($B12,INDEX('Race Resuts'!$A$2:$W$23,0,MATCH(O$1,'Race Resuts'!$A$1:$W$1,0)),0),'Points Refrence'!$A$2:$B$11,2,FALSE),0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P12" s="42">
         <f>IFERROR(VLOOKUP(MATCH($B12,INDEX('Race Resuts'!$B$2:$W$23,0,MATCH(P$1,'Race Resuts'!$B$1:$W$1,0)),0),'Points Refrence'!$A$2:$B$11,2,FALSE),0)+IFERROR(VLOOKUP(MATCH($B12,INDEX('Sprint Race Results'!$B$2:$G$23,0,MATCH(P$1,'Sprint Race Results'!$B$1:$G$1,0)),0),'Points Refrence'!$D$2:$E$9,2,FALSE),0)</f>
@@ -6294,7 +6361,7 @@
       </c>
       <c r="AB12" s="7">
         <f t="shared" si="0"/>
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AD12" s="4">
         <f t="shared" si="1"/>
@@ -6306,7 +6373,7 @@
       </c>
       <c r="AF12" s="4">
         <f t="shared" si="3"/>
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="13" spans="1:34" ht="21.6" x14ac:dyDescent="0.4">
@@ -6328,11 +6395,11 @@
         <f>IFERROR(VLOOKUP(MATCH($B13,INDEX('Race Resuts'!$A$2:$W$23,0,MATCH(E$1,'Race Resuts'!$A$1:$W$1,0)),0),'Points Refrence'!$A$2:$B$11,2,FALSE),0)</f>
         <v>2</v>
       </c>
-      <c r="F13" s="4">
+      <c r="F13" s="47">
         <f>IFERROR(VLOOKUP(MATCH($B13,INDEX('Race Resuts'!$A$2:$W$23,0,MATCH(F$1,'Race Resuts'!$A$1:$W$1,0)),0),'Points Refrence'!$A$2:$B$11,2,FALSE),0)</f>
         <v>0</v>
       </c>
-      <c r="G13" s="4">
+      <c r="G13" s="47">
         <f>IFERROR(VLOOKUP(MATCH($B13,INDEX('Race Resuts'!$A$2:$W$23,0,MATCH(G$1,'Race Resuts'!$A$1:$W$1,0)),0),'Points Refrence'!$A$2:$B$11,2,FALSE),0)</f>
         <v>0</v>
       </c>
@@ -6366,7 +6433,7 @@
       </c>
       <c r="O13" s="4">
         <f>IFERROR(VLOOKUP(MATCH($B13,INDEX('Race Resuts'!$A$2:$W$23,0,MATCH(O$1,'Race Resuts'!$A$1:$W$1,0)),0),'Points Refrence'!$A$2:$B$11,2,FALSE),0)</f>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P13" s="42">
         <f>IFERROR(VLOOKUP(MATCH($B13,INDEX('Race Resuts'!$B$2:$W$23,0,MATCH(P$1,'Race Resuts'!$B$1:$W$1,0)),0),'Points Refrence'!$A$2:$B$11,2,FALSE),0)+IFERROR(VLOOKUP(MATCH($B13,INDEX('Sprint Race Results'!$B$2:$G$23,0,MATCH(P$1,'Sprint Race Results'!$B$1:$G$1,0)),0),'Points Refrence'!$D$2:$E$9,2,FALSE),0)</f>
@@ -6414,11 +6481,11 @@
       </c>
       <c r="AA13" s="7">
         <f>RANK(AB13,$AB$2:$AB$23,0)+COUNTIF($AB$2:AB13,AB13)-1</f>
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AB13" s="7">
         <f t="shared" si="0"/>
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="AD13" s="4">
         <f t="shared" si="1"/>
@@ -6452,11 +6519,11 @@
         <f>IFERROR(VLOOKUP(MATCH($B14,INDEX('Race Resuts'!$A$2:$W$23,0,MATCH(E$1,'Race Resuts'!$A$1:$W$1,0)),0),'Points Refrence'!$A$2:$B$11,2,FALSE),0)</f>
         <v>0</v>
       </c>
-      <c r="F14" s="4">
+      <c r="F14" s="47">
         <f>IFERROR(VLOOKUP(MATCH($B14,INDEX('Race Resuts'!$A$2:$W$23,0,MATCH(F$1,'Race Resuts'!$A$1:$W$1,0)),0),'Points Refrence'!$A$2:$B$11,2,FALSE),0)</f>
         <v>0</v>
       </c>
-      <c r="G14" s="4">
+      <c r="G14" s="47">
         <f>IFERROR(VLOOKUP(MATCH($B14,INDEX('Race Resuts'!$A$2:$W$23,0,MATCH(G$1,'Race Resuts'!$A$1:$W$1,0)),0),'Points Refrence'!$A$2:$B$11,2,FALSE),0)</f>
         <v>0</v>
       </c>
@@ -6576,11 +6643,11 @@
         <f>IFERROR(VLOOKUP(MATCH($B15,INDEX('Race Resuts'!$A$2:$W$23,0,MATCH(E$1,'Race Resuts'!$A$1:$W$1,0)),0),'Points Refrence'!$A$2:$B$11,2,FALSE),0)</f>
         <v>1</v>
       </c>
-      <c r="F15" s="4">
+      <c r="F15" s="47">
         <f>IFERROR(VLOOKUP(MATCH($B15,INDEX('Race Resuts'!$A$2:$W$23,0,MATCH(F$1,'Race Resuts'!$A$1:$W$1,0)),0),'Points Refrence'!$A$2:$B$11,2,FALSE),0)</f>
         <v>0</v>
       </c>
-      <c r="G15" s="4">
+      <c r="G15" s="47">
         <f>IFERROR(VLOOKUP(MATCH($B15,INDEX('Race Resuts'!$A$2:$W$23,0,MATCH(G$1,'Race Resuts'!$A$1:$W$1,0)),0),'Points Refrence'!$A$2:$B$11,2,FALSE),0)</f>
         <v>0</v>
       </c>
@@ -6700,11 +6767,11 @@
         <f>IFERROR(VLOOKUP(MATCH($B16,INDEX('Race Resuts'!$A$2:$W$23,0,MATCH(E$1,'Race Resuts'!$A$1:$W$1,0)),0),'Points Refrence'!$A$2:$B$11,2,FALSE),0)</f>
         <v>0</v>
       </c>
-      <c r="F16" s="4">
+      <c r="F16" s="47">
         <f>IFERROR(VLOOKUP(MATCH($B16,INDEX('Race Resuts'!$A$2:$W$23,0,MATCH(F$1,'Race Resuts'!$A$1:$W$1,0)),0),'Points Refrence'!$A$2:$B$11,2,FALSE),0)</f>
         <v>0</v>
       </c>
-      <c r="G16" s="4">
+      <c r="G16" s="47">
         <f>IFERROR(VLOOKUP(MATCH($B16,INDEX('Race Resuts'!$A$2:$W$23,0,MATCH(G$1,'Race Resuts'!$A$1:$W$1,0)),0),'Points Refrence'!$A$2:$B$11,2,FALSE),0)</f>
         <v>0</v>
       </c>
@@ -6738,7 +6805,7 @@
       </c>
       <c r="O16" s="4">
         <f>IFERROR(VLOOKUP(MATCH($B16,INDEX('Race Resuts'!$A$2:$W$23,0,MATCH(O$1,'Race Resuts'!$A$1:$W$1,0)),0),'Points Refrence'!$A$2:$B$11,2,FALSE),0)</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P16" s="42">
         <f>IFERROR(VLOOKUP(MATCH($B16,INDEX('Race Resuts'!$B$2:$W$23,0,MATCH(P$1,'Race Resuts'!$B$1:$W$1,0)),0),'Points Refrence'!$A$2:$B$11,2,FALSE),0)+IFERROR(VLOOKUP(MATCH($B16,INDEX('Sprint Race Results'!$B$2:$G$23,0,MATCH(P$1,'Sprint Race Results'!$B$1:$G$1,0)),0),'Points Refrence'!$D$2:$E$9,2,FALSE),0)</f>
@@ -6786,11 +6853,11 @@
       </c>
       <c r="AA16" s="7">
         <f>RANK(AB16,$AB$2:$AB$23,0)+COUNTIF($AB$2:AB16,AB16)-1</f>
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AB16" s="7">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AD16" s="4">
         <f t="shared" si="1"/>
@@ -6824,11 +6891,11 @@
         <f>IFERROR(VLOOKUP(MATCH($B17,INDEX('Race Resuts'!$A$2:$W$23,0,MATCH(E$1,'Race Resuts'!$A$1:$W$1,0)),0),'Points Refrence'!$A$2:$B$11,2,FALSE),0)</f>
         <v>0</v>
       </c>
-      <c r="F17" s="4">
+      <c r="F17" s="47">
         <f>IFERROR(VLOOKUP(MATCH($B17,INDEX('Race Resuts'!$A$2:$W$23,0,MATCH(F$1,'Race Resuts'!$A$1:$W$1,0)),0),'Points Refrence'!$A$2:$B$11,2,FALSE),0)</f>
         <v>0</v>
       </c>
-      <c r="G17" s="4">
+      <c r="G17" s="47">
         <f>IFERROR(VLOOKUP(MATCH($B17,INDEX('Race Resuts'!$A$2:$W$23,0,MATCH(G$1,'Race Resuts'!$A$1:$W$1,0)),0),'Points Refrence'!$A$2:$B$11,2,FALSE),0)</f>
         <v>0</v>
       </c>
@@ -6948,11 +7015,11 @@
         <f>IFERROR(VLOOKUP(MATCH($B18,INDEX('Race Resuts'!$A$2:$W$23,0,MATCH(E$1,'Race Resuts'!$A$1:$W$1,0)),0),'Points Refrence'!$A$2:$B$11,2,FALSE),0)</f>
         <v>0</v>
       </c>
-      <c r="F18" s="4">
+      <c r="F18" s="47">
         <f>IFERROR(VLOOKUP(MATCH($B18,INDEX('Race Resuts'!$A$2:$W$23,0,MATCH(F$1,'Race Resuts'!$A$1:$W$1,0)),0),'Points Refrence'!$A$2:$B$11,2,FALSE),0)</f>
         <v>0</v>
       </c>
-      <c r="G18" s="4">
+      <c r="G18" s="47">
         <f>IFERROR(VLOOKUP(MATCH($B18,INDEX('Race Resuts'!$A$2:$W$23,0,MATCH(G$1,'Race Resuts'!$A$1:$W$1,0)),0),'Points Refrence'!$A$2:$B$11,2,FALSE),0)</f>
         <v>0</v>
       </c>
@@ -7072,11 +7139,11 @@
         <f>IFERROR(VLOOKUP(MATCH($B19,INDEX('Race Resuts'!$A$2:$W$23,0,MATCH(E$1,'Race Resuts'!$A$1:$W$1,0)),0),'Points Refrence'!$A$2:$B$11,2,FALSE),0)</f>
         <v>0</v>
       </c>
-      <c r="F19" s="4">
+      <c r="F19" s="47">
         <f>IFERROR(VLOOKUP(MATCH($B19,INDEX('Race Resuts'!$A$2:$W$23,0,MATCH(F$1,'Race Resuts'!$A$1:$W$1,0)),0),'Points Refrence'!$A$2:$B$11,2,FALSE),0)</f>
         <v>0</v>
       </c>
-      <c r="G19" s="4">
+      <c r="G19" s="47">
         <f>IFERROR(VLOOKUP(MATCH($B19,INDEX('Race Resuts'!$A$2:$W$23,0,MATCH(G$1,'Race Resuts'!$A$1:$W$1,0)),0),'Points Refrence'!$A$2:$B$11,2,FALSE),0)</f>
         <v>0</v>
       </c>
@@ -7170,11 +7237,11 @@
       </c>
       <c r="AE19" s="4" t="str">
         <f t="shared" si="2"/>
-        <v>ALO</v>
+        <v>HUL</v>
       </c>
       <c r="AF19" s="4">
         <f t="shared" si="3"/>
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="20" spans="1:32" ht="21.6" x14ac:dyDescent="0.4">
@@ -7196,11 +7263,11 @@
         <f>IFERROR(VLOOKUP(MATCH($B20,INDEX('Race Resuts'!$A$2:$W$23,0,MATCH(E$1,'Race Resuts'!$A$1:$W$1,0)),0),'Points Refrence'!$A$2:$B$11,2,FALSE),0)</f>
         <v>0</v>
       </c>
-      <c r="F20" s="4">
+      <c r="F20" s="47">
         <f>IFERROR(VLOOKUP(MATCH($B20,INDEX('Race Resuts'!$A$2:$W$23,0,MATCH(F$1,'Race Resuts'!$A$1:$W$1,0)),0),'Points Refrence'!$A$2:$B$11,2,FALSE),0)</f>
         <v>0</v>
       </c>
-      <c r="G20" s="4">
+      <c r="G20" s="47">
         <f>IFERROR(VLOOKUP(MATCH($B20,INDEX('Race Resuts'!$A$2:$W$23,0,MATCH(G$1,'Race Resuts'!$A$1:$W$1,0)),0),'Points Refrence'!$A$2:$B$11,2,FALSE),0)</f>
         <v>0</v>
       </c>
@@ -7282,7 +7349,7 @@
       </c>
       <c r="AA20" s="7">
         <f>RANK(AB20,$AB$2:$AB$23,0)+COUNTIF($AB$2:AB20,AB20)-1</f>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AB20" s="7">
         <f t="shared" si="0"/>
@@ -7294,11 +7361,11 @@
       </c>
       <c r="AE20" s="4" t="str">
         <f t="shared" si="2"/>
-        <v>HUL</v>
+        <v>ALO</v>
       </c>
       <c r="AF20" s="4">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="21" spans="1:32" ht="21.6" x14ac:dyDescent="0.4">
@@ -7320,11 +7387,11 @@
         <f>IFERROR(VLOOKUP(MATCH($B21,INDEX('Race Resuts'!$A$2:$W$23,0,MATCH(E$1,'Race Resuts'!$A$1:$W$1,0)),0),'Points Refrence'!$A$2:$B$11,2,FALSE),0)</f>
         <v>0</v>
       </c>
-      <c r="F21" s="4">
+      <c r="F21" s="47">
         <f>IFERROR(VLOOKUP(MATCH($B21,INDEX('Race Resuts'!$A$2:$W$23,0,MATCH(F$1,'Race Resuts'!$A$1:$W$1,0)),0),'Points Refrence'!$A$2:$B$11,2,FALSE),0)</f>
         <v>0</v>
       </c>
-      <c r="G21" s="4">
+      <c r="G21" s="47">
         <f>IFERROR(VLOOKUP(MATCH($B21,INDEX('Race Resuts'!$A$2:$W$23,0,MATCH(G$1,'Race Resuts'!$A$1:$W$1,0)),0),'Points Refrence'!$A$2:$B$11,2,FALSE),0)</f>
         <v>0</v>
       </c>
@@ -7444,11 +7511,11 @@
         <f>IFERROR(VLOOKUP(MATCH($B22,INDEX('Race Resuts'!$A$2:$W$23,0,MATCH(E$1,'Race Resuts'!$A$1:$W$1,0)),0),'Points Refrence'!$A$2:$B$11,2,FALSE),0)</f>
         <v>0</v>
       </c>
-      <c r="F22" s="4">
+      <c r="F22" s="47">
         <f>IFERROR(VLOOKUP(MATCH($B22,INDEX('Race Resuts'!$A$2:$W$23,0,MATCH(F$1,'Race Resuts'!$A$1:$W$1,0)),0),'Points Refrence'!$A$2:$B$11,2,FALSE),0)</f>
         <v>0</v>
       </c>
-      <c r="G22" s="4">
+      <c r="G22" s="47">
         <f>IFERROR(VLOOKUP(MATCH($B22,INDEX('Race Resuts'!$A$2:$W$23,0,MATCH(G$1,'Race Resuts'!$A$1:$W$1,0)),0),'Points Refrence'!$A$2:$B$11,2,FALSE),0)</f>
         <v>0</v>
       </c>
@@ -7568,11 +7635,11 @@
         <f>IFERROR(VLOOKUP(MATCH($B23,INDEX('Race Resuts'!$A$2:$W$23,0,MATCH(E$1,'Race Resuts'!$A$1:$W$1,0)),0),'Points Refrence'!$A$2:$B$11,2,FALSE),0)</f>
         <v>0</v>
       </c>
-      <c r="F23" s="4">
+      <c r="F23" s="47">
         <f>IFERROR(VLOOKUP(MATCH($B23,INDEX('Race Resuts'!$A$2:$W$23,0,MATCH(F$1,'Race Resuts'!$A$1:$W$1,0)),0),'Points Refrence'!$A$2:$B$11,2,FALSE),0)</f>
         <v>0</v>
       </c>
-      <c r="G23" s="4">
+      <c r="G23" s="47">
         <f>IFERROR(VLOOKUP(MATCH($B23,INDEX('Race Resuts'!$A$2:$W$23,0,MATCH(G$1,'Race Resuts'!$A$1:$W$1,0)),0),'Points Refrence'!$A$2:$B$11,2,FALSE),0)</f>
         <v>0</v>
       </c>
@@ -7679,8 +7746,9 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
   <tableParts count="1">
-    <tablePart r:id="rId1"/>
+    <tablePart r:id="rId2"/>
   </tableParts>
 </worksheet>
 </file>
@@ -7710,10 +7778,10 @@
       <c r="D1" s="23" t="s">
         <v>18</v>
       </c>
-      <c r="E1" s="23" t="s">
+      <c r="E1" s="49" t="s">
         <v>19</v>
       </c>
-      <c r="F1" s="23" t="s">
+      <c r="F1" s="49" t="s">
         <v>20</v>
       </c>
       <c r="G1" s="23" t="s">
@@ -7805,11 +7873,11 @@
         <f>IFERROR(INDEX('Drivers'' Standings'!$C:$Z,MATCH("RUS",'Drivers'' Standings'!$B:$B,0),MATCH(D$1,'Drivers'' Standings'!$C$1:$Z$1,0))+INDEX('Drivers'' Standings'!$C:$Z,MATCH("ANT",'Drivers'' Standings'!$B:$B,0),MATCH(D$1,'Drivers'' Standings'!$C$1:$Z$1,0)),0)</f>
         <v>37</v>
       </c>
-      <c r="E2" s="25">
+      <c r="E2" s="50">
         <f>IFERROR(INDEX('Drivers'' Standings'!$C:$Z,MATCH("RUS",'Drivers'' Standings'!$B:$B,0),MATCH(E$1,'Drivers'' Standings'!$C$1:$Z$1,0))+INDEX('Drivers'' Standings'!$C:$Z,MATCH("ANT",'Drivers'' Standings'!$B:$B,0),MATCH(E$1,'Drivers'' Standings'!$C$1:$Z$1,0)),0)</f>
         <v>0</v>
       </c>
-      <c r="F2" s="25">
+      <c r="F2" s="50">
         <f>IFERROR(INDEX('Drivers'' Standings'!$C:$Z,MATCH("RUS",'Drivers'' Standings'!$B:$B,0),MATCH(F$1,'Drivers'' Standings'!$C$1:$Z$1,0))+INDEX('Drivers'' Standings'!$C:$Z,MATCH("ANT",'Drivers'' Standings'!$B:$B,0),MATCH(F$1,'Drivers'' Standings'!$C$1:$Z$1,0)),0)</f>
         <v>0</v>
       </c>
@@ -7843,7 +7911,7 @@
       </c>
       <c r="N2" s="25">
         <f>IFERROR(INDEX('Drivers'' Standings'!$C:$Z,MATCH("RUS",'Drivers'' Standings'!$B:$B,0),MATCH(N$1,'Drivers'' Standings'!$C$1:$Z$1,0))+INDEX('Drivers'' Standings'!$C:$Z,MATCH("ANT",'Drivers'' Standings'!$B:$B,0),MATCH(N$1,'Drivers'' Standings'!$C$1:$Z$1,0)),0)</f>
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="O2" s="25">
         <f>IFERROR(INDEX('Drivers'' Standings'!$C:$Z,MATCH("RUS",'Drivers'' Standings'!$B:$B,0),MATCH(O$1,'Drivers'' Standings'!$C$1:$Z$1,0))+INDEX('Drivers'' Standings'!$C:$Z,MATCH("ANT",'Drivers'' Standings'!$B:$B,0),MATCH(O$1,'Drivers'' Standings'!$C$1:$Z$1,0)),0)</f>
@@ -7891,7 +7959,7 @@
       </c>
       <c r="Z2" s="25">
         <f t="shared" ref="Z2:Z12" si="0">SUM(B2:Y2)</f>
-        <v>358</v>
+        <v>379</v>
       </c>
       <c r="AB2" s="39">
         <f>ROW()-1</f>
@@ -7903,7 +7971,7 @@
       </c>
       <c r="AD2" s="21" cm="1">
         <f t="array" ref="AD2">INDEX($Z$2:$Z$12,MATCH(LARGE($Z$2:$Z$12+ROW($Z$2:$Z$12)/100000,ROW()-1),$Z$2:$Z$12+ROW($Z$2:$Z$12)/100000,0))</f>
-        <v>358</v>
+        <v>379</v>
       </c>
     </row>
     <row r="3" spans="1:32" ht="21.6" x14ac:dyDescent="0.4">
@@ -7922,11 +7990,11 @@
         <f>IFERROR(INDEX('Drivers'' Standings'!$C:$Z,MATCH("HAM",'Drivers'' Standings'!$B:$B,0),MATCH(D$1,'Drivers'' Standings'!$C$1:$Z$1,0))+INDEX('Drivers'' Standings'!$C:$Z,MATCH("LEC",'Drivers'' Standings'!$B:$B,0),MATCH(D$1,'Drivers'' Standings'!$C$1:$Z$1,0)),0)</f>
         <v>23</v>
       </c>
-      <c r="E3" s="27">
+      <c r="E3" s="51">
         <f>IFERROR(INDEX('Drivers'' Standings'!$C:$Z,MATCH("HAM",'Drivers'' Standings'!$B:$B,0),MATCH(E$1,'Drivers'' Standings'!$C$1:$Z$1,0))+INDEX('Drivers'' Standings'!$C:$Z,MATCH("LEC",'Drivers'' Standings'!$B:$B,0),MATCH(E$1,'Drivers'' Standings'!$C$1:$Z$1,0)),0)</f>
         <v>0</v>
       </c>
-      <c r="F3" s="27">
+      <c r="F3" s="51">
         <f>IFERROR(INDEX('Drivers'' Standings'!$C:$Z,MATCH("HAM",'Drivers'' Standings'!$B:$B,0),MATCH(F$1,'Drivers'' Standings'!$C$1:$Z$1,0))+INDEX('Drivers'' Standings'!$C:$Z,MATCH("LEC",'Drivers'' Standings'!$B:$B,0),MATCH(F$1,'Drivers'' Standings'!$C$1:$Z$1,0)),0)</f>
         <v>0</v>
       </c>
@@ -7960,7 +8028,7 @@
       </c>
       <c r="N3" s="27">
         <f>IFERROR(INDEX('Drivers'' Standings'!$C:$Z,MATCH("HAM",'Drivers'' Standings'!$B:$B,0),MATCH(N$1,'Drivers'' Standings'!$C$1:$Z$1,0))+INDEX('Drivers'' Standings'!$C:$Z,MATCH("LEC",'Drivers'' Standings'!$B:$B,0),MATCH(N$1,'Drivers'' Standings'!$C$1:$Z$1,0)),0)</f>
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="O3" s="27">
         <f>IFERROR(INDEX('Drivers'' Standings'!$C:$Z,MATCH("HAM",'Drivers'' Standings'!$B:$B,0),MATCH(O$1,'Drivers'' Standings'!$C$1:$Z$1,0))+INDEX('Drivers'' Standings'!$C:$Z,MATCH("LEC",'Drivers'' Standings'!$B:$B,0),MATCH(O$1,'Drivers'' Standings'!$C$1:$Z$1,0)),0)</f>
@@ -8008,7 +8076,7 @@
       </c>
       <c r="Z3" s="27">
         <f t="shared" si="0"/>
-        <v>285</v>
+        <v>307</v>
       </c>
       <c r="AB3" s="39">
         <f t="shared" ref="AB3:AB12" si="1">ROW()-1</f>
@@ -8020,7 +8088,7 @@
       </c>
       <c r="AD3" s="21" cm="1">
         <f t="array" ref="AD3">INDEX($Z$2:$Z$12,MATCH(LARGE($Z$2:$Z$12+ROW($Z$2:$Z$12)/100000,ROW()-1),$Z$2:$Z$12+ROW($Z$2:$Z$12)/100000,0))</f>
-        <v>285</v>
+        <v>307</v>
       </c>
     </row>
     <row r="4" spans="1:32" ht="21.6" x14ac:dyDescent="0.4">
@@ -8039,11 +8107,11 @@
         <f>IFERROR(INDEX('Drivers'' Standings'!$C:$Z,MATCH("NOR",'Drivers'' Standings'!$B:$B,0),MATCH(D$1,'Drivers'' Standings'!$C$1:$Z$1,0))+INDEX('Drivers'' Standings'!$C:$Z,MATCH("PIA",'Drivers'' Standings'!$B:$B,0),MATCH(D$1,'Drivers'' Standings'!$C$1:$Z$1,0)),0)</f>
         <v>28</v>
       </c>
-      <c r="E4" s="25">
+      <c r="E4" s="50">
         <f>IFERROR(INDEX('Drivers'' Standings'!$C:$Z,MATCH("NOR",'Drivers'' Standings'!$B:$B,0),MATCH(E$1,'Drivers'' Standings'!$C$1:$Z$1,0))+INDEX('Drivers'' Standings'!$C:$Z,MATCH("PIA",'Drivers'' Standings'!$B:$B,0),MATCH(E$1,'Drivers'' Standings'!$C$1:$Z$1,0)),0)</f>
         <v>0</v>
       </c>
-      <c r="F4" s="25">
+      <c r="F4" s="50">
         <f>IFERROR(INDEX('Drivers'' Standings'!$C:$Z,MATCH("NOR",'Drivers'' Standings'!$B:$B,0),MATCH(F$1,'Drivers'' Standings'!$C$1:$Z$1,0))+INDEX('Drivers'' Standings'!$C:$Z,MATCH("PIA",'Drivers'' Standings'!$B:$B,0),MATCH(F$1,'Drivers'' Standings'!$C$1:$Z$1,0)),0)</f>
         <v>0</v>
       </c>
@@ -8077,7 +8145,7 @@
       </c>
       <c r="N4" s="25">
         <f>IFERROR(INDEX('Drivers'' Standings'!$C:$Z,MATCH("NOR",'Drivers'' Standings'!$B:$B,0),MATCH(N$1,'Drivers'' Standings'!$C$1:$Z$1,0))+INDEX('Drivers'' Standings'!$C:$Z,MATCH("PIA",'Drivers'' Standings'!$B:$B,0),MATCH(N$1,'Drivers'' Standings'!$C$1:$Z$1,0)),0)</f>
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="O4" s="25">
         <f>IFERROR(INDEX('Drivers'' Standings'!$C:$Z,MATCH("NOR",'Drivers'' Standings'!$B:$B,0),MATCH(O$1,'Drivers'' Standings'!$C$1:$Z$1,0))+INDEX('Drivers'' Standings'!$C:$Z,MATCH("PIA",'Drivers'' Standings'!$B:$B,0),MATCH(O$1,'Drivers'' Standings'!$C$1:$Z$1,0)),0)</f>
@@ -8125,7 +8193,7 @@
       </c>
       <c r="Z4" s="25">
         <f t="shared" si="0"/>
-        <v>195</v>
+        <v>220</v>
       </c>
       <c r="AB4" s="39">
         <f t="shared" si="1"/>
@@ -8137,7 +8205,7 @@
       </c>
       <c r="AD4" s="21" cm="1">
         <f t="array" ref="AD4">INDEX($Z$2:$Z$12,MATCH(LARGE($Z$2:$Z$12+ROW($Z$2:$Z$12)/100000,ROW()-1),$Z$2:$Z$12+ROW($Z$2:$Z$12)/100000,0))</f>
-        <v>195</v>
+        <v>220</v>
       </c>
     </row>
     <row r="5" spans="1:32" ht="21.6" x14ac:dyDescent="0.4">
@@ -8156,11 +8224,11 @@
         <f>IFERROR(INDEX('Drivers'' Standings'!$C:$Z,MATCH("VER",'Drivers'' Standings'!$B:$B,0),MATCH(D$1,'Drivers'' Standings'!$C$1:$Z$1,0))+INDEX('Drivers'' Standings'!$C:$Z,MATCH("HAD",'Drivers'' Standings'!$B:$B,0),MATCH(D$1,'Drivers'' Standings'!$C$1:$Z$1,0)),0)</f>
         <v>4</v>
       </c>
-      <c r="E5" s="27">
+      <c r="E5" s="51">
         <f>IFERROR(INDEX('Drivers'' Standings'!$C:$Z,MATCH("VER",'Drivers'' Standings'!$B:$B,0),MATCH(E$1,'Drivers'' Standings'!$C$1:$Z$1,0))+INDEX('Drivers'' Standings'!$C:$Z,MATCH("HAD",'Drivers'' Standings'!$B:$B,0),MATCH(E$1,'Drivers'' Standings'!$C$1:$Z$1,0)),0)</f>
         <v>0</v>
       </c>
-      <c r="F5" s="27">
+      <c r="F5" s="51">
         <f>IFERROR(INDEX('Drivers'' Standings'!$C:$Z,MATCH("VER",'Drivers'' Standings'!$B:$B,0),MATCH(F$1,'Drivers'' Standings'!$C$1:$Z$1,0))+INDEX('Drivers'' Standings'!$C:$Z,MATCH("HAD",'Drivers'' Standings'!$B:$B,0),MATCH(F$1,'Drivers'' Standings'!$C$1:$Z$1,0)),0)</f>
         <v>0</v>
       </c>
@@ -8194,7 +8262,7 @@
       </c>
       <c r="N5" s="27">
         <f>IFERROR(INDEX('Drivers'' Standings'!$C:$Z,MATCH("VER",'Drivers'' Standings'!$B:$B,0),MATCH(N$1,'Drivers'' Standings'!$C$1:$Z$1,0))+INDEX('Drivers'' Standings'!$C:$Z,MATCH("HAD",'Drivers'' Standings'!$B:$B,0),MATCH(N$1,'Drivers'' Standings'!$C$1:$Z$1,0)),0)</f>
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="O5" s="27">
         <f>IFERROR(INDEX('Drivers'' Standings'!$C:$Z,MATCH("VER",'Drivers'' Standings'!$B:$B,0),MATCH(O$1,'Drivers'' Standings'!$C$1:$Z$1,0))+INDEX('Drivers'' Standings'!$C:$Z,MATCH("HAD",'Drivers'' Standings'!$B:$B,0),MATCH(O$1,'Drivers'' Standings'!$C$1:$Z$1,0)),0)</f>
@@ -8242,7 +8310,7 @@
       </c>
       <c r="Z5" s="27">
         <f t="shared" si="0"/>
-        <v>151</v>
+        <v>177</v>
       </c>
       <c r="AB5" s="39">
         <f t="shared" si="1"/>
@@ -8254,7 +8322,7 @@
       </c>
       <c r="AD5" s="21" cm="1">
         <f t="array" ref="AD5">INDEX($Z$2:$Z$12,MATCH(LARGE($Z$2:$Z$12+ROW($Z$2:$Z$12)/100000,ROW()-1),$Z$2:$Z$12+ROW($Z$2:$Z$12)/100000,0))</f>
-        <v>151</v>
+        <v>177</v>
       </c>
     </row>
     <row r="6" spans="1:32" ht="21.6" x14ac:dyDescent="0.4">
@@ -8273,11 +8341,11 @@
         <f>IFERROR(INDEX('Drivers'' Standings'!$C:$Z,MATCH("OCO",'Drivers'' Standings'!$B:$B,0),MATCH(D$1,'Drivers'' Standings'!$C$1:$Z$1,0))+INDEX('Drivers'' Standings'!$C:$Z,MATCH("BEA",'Drivers'' Standings'!$B:$B,0),MATCH(D$1,'Drivers'' Standings'!$C$1:$Z$1,0)),0)</f>
         <v>1</v>
       </c>
-      <c r="E6" s="25">
+      <c r="E6" s="50">
         <f>IFERROR(INDEX('Drivers'' Standings'!$C:$Z,MATCH("OCO",'Drivers'' Standings'!$B:$B,0),MATCH(E$1,'Drivers'' Standings'!$C$1:$Z$1,0))+INDEX('Drivers'' Standings'!$C:$Z,MATCH("BEA",'Drivers'' Standings'!$B:$B,0),MATCH(E$1,'Drivers'' Standings'!$C$1:$Z$1,0)),0)</f>
         <v>0</v>
       </c>
-      <c r="F6" s="25">
+      <c r="F6" s="50">
         <f>IFERROR(INDEX('Drivers'' Standings'!$C:$Z,MATCH("OCO",'Drivers'' Standings'!$B:$B,0),MATCH(F$1,'Drivers'' Standings'!$C$1:$Z$1,0))+INDEX('Drivers'' Standings'!$C:$Z,MATCH("BEA",'Drivers'' Standings'!$B:$B,0),MATCH(F$1,'Drivers'' Standings'!$C$1:$Z$1,0)),0)</f>
         <v>0</v>
       </c>
@@ -8367,11 +8435,11 @@
       </c>
       <c r="AC6" s="21" t="str" cm="1">
         <f t="array" ref="AC6">INDEX($A$2:$A$12,MATCH(LARGE($Z$2:$Z$12+ROW($Z$2:$Z$12)/100000,ROW()-1),$Z$2:$Z$12+ROW($Z$2:$Z$12)/100000,0))</f>
-        <v>Alpine</v>
+        <v>Racing Bulls</v>
       </c>
       <c r="AD6" s="21" cm="1">
         <f t="array" ref="AD6">INDEX($Z$2:$Z$12,MATCH(LARGE($Z$2:$Z$12+ROW($Z$2:$Z$12)/100000,ROW()-1),$Z$2:$Z$12+ROW($Z$2:$Z$12)/100000,0))</f>
-        <v>61</v>
+        <v>66</v>
       </c>
     </row>
     <row r="7" spans="1:32" ht="21.6" x14ac:dyDescent="0.4">
@@ -8390,11 +8458,11 @@
         <f>IFERROR(INDEX('Drivers'' Standings'!$C:$Z,MATCH("LAW",'Drivers'' Standings'!$B:$B,0),MATCH(D$1,'Drivers'' Standings'!$C$1:$Z$1,0))+INDEX('Drivers'' Standings'!$C:$Z,MATCH("LIN",'Drivers'' Standings'!$B:$B,0),MATCH(D$1,'Drivers'' Standings'!$C$1:$Z$1,0)),0)</f>
         <v>2</v>
       </c>
-      <c r="E7" s="27">
+      <c r="E7" s="51">
         <f>IFERROR(INDEX('Drivers'' Standings'!$C:$Z,MATCH("LAW",'Drivers'' Standings'!$B:$B,0),MATCH(E$1,'Drivers'' Standings'!$C$1:$Z$1,0))+INDEX('Drivers'' Standings'!$C:$Z,MATCH("LIN",'Drivers'' Standings'!$B:$B,0),MATCH(E$1,'Drivers'' Standings'!$C$1:$Z$1,0)),0)</f>
         <v>0</v>
       </c>
-      <c r="F7" s="27">
+      <c r="F7" s="51">
         <f>IFERROR(INDEX('Drivers'' Standings'!$C:$Z,MATCH("LAW",'Drivers'' Standings'!$B:$B,0),MATCH(F$1,'Drivers'' Standings'!$C$1:$Z$1,0))+INDEX('Drivers'' Standings'!$C:$Z,MATCH("LIN",'Drivers'' Standings'!$B:$B,0),MATCH(F$1,'Drivers'' Standings'!$C$1:$Z$1,0)),0)</f>
         <v>0</v>
       </c>
@@ -8428,7 +8496,7 @@
       </c>
       <c r="N7" s="27">
         <f>IFERROR(INDEX('Drivers'' Standings'!$C:$Z,MATCH("LAW",'Drivers'' Standings'!$B:$B,0),MATCH(N$1,'Drivers'' Standings'!$C$1:$Z$1,0))+INDEX('Drivers'' Standings'!$C:$Z,MATCH("LIN",'Drivers'' Standings'!$B:$B,0),MATCH(N$1,'Drivers'' Standings'!$C$1:$Z$1,0)),0)</f>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="O7" s="27">
         <f>IFERROR(INDEX('Drivers'' Standings'!$C:$Z,MATCH("LAW",'Drivers'' Standings'!$B:$B,0),MATCH(O$1,'Drivers'' Standings'!$C$1:$Z$1,0))+INDEX('Drivers'' Standings'!$C:$Z,MATCH("LIN",'Drivers'' Standings'!$B:$B,0),MATCH(O$1,'Drivers'' Standings'!$C$1:$Z$1,0)),0)</f>
@@ -8476,7 +8544,7 @@
       </c>
       <c r="Z7" s="27">
         <f t="shared" si="0"/>
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="AB7" s="39">
         <f t="shared" si="1"/>
@@ -8484,7 +8552,7 @@
       </c>
       <c r="AC7" s="21" t="str" cm="1">
         <f t="array" ref="AC7">INDEX($A$2:$A$12,MATCH(LARGE($Z$2:$Z$12+ROW($Z$2:$Z$12)/100000,ROW()-1),$Z$2:$Z$12+ROW($Z$2:$Z$12)/100000,0))</f>
-        <v>Racing Bulls</v>
+        <v>Alpine</v>
       </c>
       <c r="AD7" s="21" cm="1">
         <f t="array" ref="AD7">INDEX($Z$2:$Z$12,MATCH(LARGE($Z$2:$Z$12+ROW($Z$2:$Z$12)/100000,ROW()-1),$Z$2:$Z$12+ROW($Z$2:$Z$12)/100000,0))</f>
@@ -8507,11 +8575,11 @@
         <f>IFERROR(INDEX('Drivers'' Standings'!$C:$Z,MATCH("HUL",'Drivers'' Standings'!$B:$B,0),MATCH(D$1,'Drivers'' Standings'!$C$1:$Z$1,0))+INDEX('Drivers'' Standings'!$C:$Z,MATCH("BOR",'Drivers'' Standings'!$B:$B,0),MATCH(D$1,'Drivers'' Standings'!$C$1:$Z$1,0)),0)</f>
         <v>0</v>
       </c>
-      <c r="E8" s="25">
+      <c r="E8" s="50">
         <f>IFERROR(INDEX('Drivers'' Standings'!$C:$Z,MATCH("HUL",'Drivers'' Standings'!$B:$B,0),MATCH(E$1,'Drivers'' Standings'!$C$1:$Z$1,0))+INDEX('Drivers'' Standings'!$C:$Z,MATCH("BOR",'Drivers'' Standings'!$B:$B,0),MATCH(E$1,'Drivers'' Standings'!$C$1:$Z$1,0)),0)</f>
         <v>0</v>
       </c>
-      <c r="F8" s="25">
+      <c r="F8" s="50">
         <f>IFERROR(INDEX('Drivers'' Standings'!$C:$Z,MATCH("HUL",'Drivers'' Standings'!$B:$B,0),MATCH(F$1,'Drivers'' Standings'!$C$1:$Z$1,0))+INDEX('Drivers'' Standings'!$C:$Z,MATCH("BOR",'Drivers'' Standings'!$B:$B,0),MATCH(F$1,'Drivers'' Standings'!$C$1:$Z$1,0)),0)</f>
         <v>0</v>
       </c>
@@ -8545,7 +8613,7 @@
       </c>
       <c r="N8" s="25">
         <f>IFERROR(INDEX('Drivers'' Standings'!$C:$Z,MATCH("HUL",'Drivers'' Standings'!$B:$B,0),MATCH(N$1,'Drivers'' Standings'!$C$1:$Z$1,0))+INDEX('Drivers'' Standings'!$C:$Z,MATCH("BOR",'Drivers'' Standings'!$B:$B,0),MATCH(N$1,'Drivers'' Standings'!$C$1:$Z$1,0)),0)</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O8" s="25">
         <f>IFERROR(INDEX('Drivers'' Standings'!$C:$Z,MATCH("HUL",'Drivers'' Standings'!$B:$B,0),MATCH(O$1,'Drivers'' Standings'!$C$1:$Z$1,0))+INDEX('Drivers'' Standings'!$C:$Z,MATCH("BOR",'Drivers'' Standings'!$B:$B,0),MATCH(O$1,'Drivers'' Standings'!$C$1:$Z$1,0)),0)</f>
@@ -8593,7 +8661,7 @@
       </c>
       <c r="Z8" s="25">
         <f t="shared" si="0"/>
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AB8" s="39">
         <f t="shared" si="1"/>
@@ -8624,11 +8692,11 @@
         <f>IFERROR(INDEX('Drivers'' Standings'!$C:$Z,MATCH("GAS",'Drivers'' Standings'!$B:$B,0),MATCH(D$1,'Drivers'' Standings'!$C$1:$Z$1,0))+INDEX('Drivers'' Standings'!$C:$Z,MATCH("COL",'Drivers'' Standings'!$B:$B,0),MATCH(D$1,'Drivers'' Standings'!$C$1:$Z$1,0)),0)</f>
         <v>6</v>
       </c>
-      <c r="E9" s="27">
+      <c r="E9" s="51">
         <f>IFERROR(INDEX('Drivers'' Standings'!$C:$Z,MATCH("GAS",'Drivers'' Standings'!$B:$B,0),MATCH(E$1,'Drivers'' Standings'!$C$1:$Z$1,0))+INDEX('Drivers'' Standings'!$C:$Z,MATCH("COL",'Drivers'' Standings'!$B:$B,0),MATCH(E$1,'Drivers'' Standings'!$C$1:$Z$1,0)),0)</f>
         <v>0</v>
       </c>
-      <c r="F9" s="27">
+      <c r="F9" s="51">
         <f>IFERROR(INDEX('Drivers'' Standings'!$C:$Z,MATCH("GAS",'Drivers'' Standings'!$B:$B,0),MATCH(F$1,'Drivers'' Standings'!$C$1:$Z$1,0))+INDEX('Drivers'' Standings'!$C:$Z,MATCH("COL",'Drivers'' Standings'!$B:$B,0),MATCH(F$1,'Drivers'' Standings'!$C$1:$Z$1,0)),0)</f>
         <v>0</v>
       </c>
@@ -8718,11 +8786,11 @@
       </c>
       <c r="AC9" s="21" t="str" cm="1">
         <f t="array" ref="AC9">INDEX($A$2:$A$12,MATCH(LARGE($Z$2:$Z$12+ROW($Z$2:$Z$12)/100000,ROW()-1),$Z$2:$Z$12+ROW($Z$2:$Z$12)/100000,0))</f>
-        <v>Williams</v>
+        <v>Audi</v>
       </c>
       <c r="AD9" s="21" cm="1">
         <f t="array" ref="AD9">INDEX($Z$2:$Z$12,MATCH(LARGE($Z$2:$Z$12+ROW($Z$2:$Z$12)/100000,ROW()-1),$Z$2:$Z$12+ROW($Z$2:$Z$12)/100000,0))</f>
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="10" spans="1:32" ht="21.6" x14ac:dyDescent="0.4">
@@ -8741,11 +8809,11 @@
         <f>IFERROR(INDEX('Drivers'' Standings'!$C:$Z,MATCH("SAI",'Drivers'' Standings'!$B:$B,0),MATCH(D$1,'Drivers'' Standings'!$C$1:$Z$1,0))+INDEX('Drivers'' Standings'!$C:$Z,MATCH("ALB",'Drivers'' Standings'!$B:$B,0),MATCH(D$1,'Drivers'' Standings'!$C$1:$Z$1,0)),0)</f>
         <v>0</v>
       </c>
-      <c r="E10" s="25">
+      <c r="E10" s="50">
         <f>IFERROR(INDEX('Drivers'' Standings'!$C:$Z,MATCH("SAI",'Drivers'' Standings'!$B:$B,0),MATCH(E$1,'Drivers'' Standings'!$C$1:$Z$1,0))+INDEX('Drivers'' Standings'!$C:$Z,MATCH("ALB",'Drivers'' Standings'!$B:$B,0),MATCH(E$1,'Drivers'' Standings'!$C$1:$Z$1,0)),0)</f>
         <v>0</v>
       </c>
-      <c r="F10" s="25">
+      <c r="F10" s="50">
         <f>IFERROR(INDEX('Drivers'' Standings'!$C:$Z,MATCH("SAI",'Drivers'' Standings'!$B:$B,0),MATCH(F$1,'Drivers'' Standings'!$C$1:$Z$1,0))+INDEX('Drivers'' Standings'!$C:$Z,MATCH("ALB",'Drivers'' Standings'!$B:$B,0),MATCH(F$1,'Drivers'' Standings'!$C$1:$Z$1,0)),0)</f>
         <v>0</v>
       </c>
@@ -8835,11 +8903,11 @@
       </c>
       <c r="AC10" s="21" t="str" cm="1">
         <f t="array" ref="AC10">INDEX($A$2:$A$12,MATCH(LARGE($Z$2:$Z$12+ROW($Z$2:$Z$12)/100000,ROW()-1),$Z$2:$Z$12+ROW($Z$2:$Z$12)/100000,0))</f>
-        <v>Audi</v>
+        <v>Williams</v>
       </c>
       <c r="AD10" s="21" cm="1">
         <f t="array" ref="AD10">INDEX($Z$2:$Z$12,MATCH(LARGE($Z$2:$Z$12+ROW($Z$2:$Z$12)/100000,ROW()-1),$Z$2:$Z$12+ROW($Z$2:$Z$12)/100000,0))</f>
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="11" spans="1:32" ht="21.6" x14ac:dyDescent="0.4">
@@ -8858,11 +8926,11 @@
         <f>IFERROR(INDEX('Drivers'' Standings'!$C:$Z,MATCH("ALO",'Drivers'' Standings'!$B:$B,0),MATCH(D$1,'Drivers'' Standings'!$C$1:$Z$1,0))+INDEX('Drivers'' Standings'!$C:$Z,MATCH("STR",'Drivers'' Standings'!$B:$B,0),MATCH(D$1,'Drivers'' Standings'!$C$1:$Z$1,0)),0)</f>
         <v>0</v>
       </c>
-      <c r="E11" s="27">
+      <c r="E11" s="51">
         <f>IFERROR(INDEX('Drivers'' Standings'!$C:$Z,MATCH("ALO",'Drivers'' Standings'!$B:$B,0),MATCH(E$1,'Drivers'' Standings'!$C$1:$Z$1,0))+INDEX('Drivers'' Standings'!$C:$Z,MATCH("STR",'Drivers'' Standings'!$B:$B,0),MATCH(E$1,'Drivers'' Standings'!$C$1:$Z$1,0)),0)</f>
         <v>0</v>
       </c>
-      <c r="F11" s="27">
+      <c r="F11" s="51">
         <f>IFERROR(INDEX('Drivers'' Standings'!$C:$Z,MATCH("ALO",'Drivers'' Standings'!$B:$B,0),MATCH(F$1,'Drivers'' Standings'!$C$1:$Z$1,0))+INDEX('Drivers'' Standings'!$C:$Z,MATCH("STR",'Drivers'' Standings'!$B:$B,0),MATCH(F$1,'Drivers'' Standings'!$C$1:$Z$1,0)),0)</f>
         <v>0</v>
       </c>
@@ -8975,11 +9043,11 @@
         <f>IFERROR(INDEX('Drivers'' Standings'!$C:$Z,MATCH("BOT",'Drivers'' Standings'!$B:$B,0),MATCH(D$1,'Drivers'' Standings'!$C$1:$Z$1,0))+INDEX('Drivers'' Standings'!$C:$Z,MATCH("PER",'Drivers'' Standings'!$B:$B,0),MATCH(D$1,'Drivers'' Standings'!$C$1:$Z$1,0)),0)</f>
         <v>0</v>
       </c>
-      <c r="E12" s="36">
+      <c r="E12" s="52">
         <f>IFERROR(INDEX('Drivers'' Standings'!$C:$Z,MATCH("BOT",'Drivers'' Standings'!$B:$B,0),MATCH(E$1,'Drivers'' Standings'!$C$1:$Z$1,0))+INDEX('Drivers'' Standings'!$C:$Z,MATCH("PER",'Drivers'' Standings'!$B:$B,0),MATCH(E$1,'Drivers'' Standings'!$C$1:$Z$1,0)),0)</f>
         <v>0</v>
       </c>
-      <c r="F12" s="36">
+      <c r="F12" s="52">
         <f>IFERROR(INDEX('Drivers'' Standings'!$C:$Z,MATCH("BOT",'Drivers'' Standings'!$B:$B,0),MATCH(F$1,'Drivers'' Standings'!$C$1:$Z$1,0))+INDEX('Drivers'' Standings'!$C:$Z,MATCH("PER",'Drivers'' Standings'!$B:$B,0),MATCH(F$1,'Drivers'' Standings'!$C$1:$Z$1,0)),0)</f>
         <v>0</v>
       </c>
@@ -9101,83 +9169,83 @@
   <sheetData>
     <row r="1" spans="1:27" ht="16.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="1"/>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="56" t="s">
         <v>16</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="56" t="s">
         <v>17</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="56" t="s">
         <v>18</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="57" t="s">
         <v>19</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="57" t="s">
         <v>20</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="G1" s="56" t="s">
         <v>21</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="H1" s="56" t="s">
         <v>22</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="I1" s="56" t="s">
         <v>23</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="J1" s="56" t="s">
         <v>24</v>
       </c>
-      <c r="K1" s="2" t="s">
+      <c r="K1" s="56" t="s">
         <v>25</v>
       </c>
-      <c r="L1" s="2" t="s">
+      <c r="L1" s="56" t="s">
         <v>26</v>
       </c>
-      <c r="M1" s="2" t="s">
+      <c r="M1" s="56" t="s">
         <v>27</v>
       </c>
-      <c r="N1" s="2" t="s">
+      <c r="N1" s="56" t="s">
         <v>28</v>
       </c>
-      <c r="O1" s="2" t="s">
+      <c r="O1" s="56" t="s">
         <v>29</v>
       </c>
-      <c r="P1" s="2" t="s">
+      <c r="P1" s="56" t="s">
         <v>30</v>
       </c>
-      <c r="Q1" s="2" t="s">
+      <c r="Q1" s="56" t="s">
         <v>31</v>
       </c>
-      <c r="R1" s="2" t="s">
+      <c r="R1" s="56" t="s">
         <v>32</v>
       </c>
-      <c r="S1" s="2" t="s">
+      <c r="S1" s="56" t="s">
         <v>33</v>
       </c>
-      <c r="T1" s="2" t="s">
+      <c r="T1" s="56" t="s">
         <v>34</v>
       </c>
-      <c r="U1" s="2" t="s">
+      <c r="U1" s="56" t="s">
         <v>35</v>
       </c>
-      <c r="V1" s="2" t="s">
+      <c r="V1" s="56" t="s">
         <v>36</v>
       </c>
-      <c r="W1" s="2" t="s">
+      <c r="W1" s="56" t="s">
         <v>37</v>
       </c>
-      <c r="X1" s="2" t="s">
+      <c r="X1" s="56" t="s">
         <v>38</v>
       </c>
-      <c r="Y1" s="2" t="s">
+      <c r="Y1" s="56" t="s">
         <v>39</v>
       </c>
       <c r="Z1" s="4"/>
       <c r="AA1" s="4"/>
     </row>
     <row r="2" spans="1:27" ht="16.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A2" s="2">
+      <c r="A2" s="54">
         <v>1</v>
       </c>
       <c r="B2" s="4" t="s">
@@ -9189,10 +9257,10 @@
       <c r="D2" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="E2" s="4" t="s">
+      <c r="E2" s="53" t="s">
         <v>40</v>
       </c>
-      <c r="F2" s="4" t="s">
+      <c r="F2" s="53" t="s">
         <v>40</v>
       </c>
       <c r="G2" s="4" t="s">
@@ -9216,7 +9284,9 @@
       <c r="M2" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="N2" s="4"/>
+      <c r="N2" s="4" t="s">
+        <v>45</v>
+      </c>
       <c r="O2" s="4"/>
       <c r="P2" s="4"/>
       <c r="Q2" s="4"/>
@@ -9232,7 +9302,7 @@
       <c r="AA2" s="4"/>
     </row>
     <row r="3" spans="1:27" ht="16.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A3" s="2">
+      <c r="A3" s="17">
         <v>2</v>
       </c>
       <c r="B3" s="4" t="s">
@@ -9244,10 +9314,10 @@
       <c r="D3" s="4" t="s">
         <v>52</v>
       </c>
-      <c r="E3" s="4" t="s">
+      <c r="E3" s="53" t="s">
         <v>40</v>
       </c>
-      <c r="F3" s="4" t="s">
+      <c r="F3" s="53" t="s">
         <v>40</v>
       </c>
       <c r="G3" s="4" t="s">
@@ -9271,7 +9341,9 @@
       <c r="M3" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="N3" s="4"/>
+      <c r="N3" s="4" t="s">
+        <v>60</v>
+      </c>
       <c r="O3" s="4"/>
       <c r="P3" s="4"/>
       <c r="Q3" s="4"/>
@@ -9287,7 +9359,7 @@
       <c r="AA3" s="4"/>
     </row>
     <row r="4" spans="1:27" ht="16.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A4" s="2">
+      <c r="A4" s="55">
         <v>3</v>
       </c>
       <c r="B4" s="4" t="s">
@@ -9299,10 +9371,10 @@
       <c r="D4" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="E4" s="4" t="s">
+      <c r="E4" s="53" t="s">
         <v>40</v>
       </c>
-      <c r="F4" s="4" t="s">
+      <c r="F4" s="53" t="s">
         <v>40</v>
       </c>
       <c r="G4" s="4" t="s">
@@ -9326,7 +9398,9 @@
       <c r="M4" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="N4" s="4"/>
+      <c r="N4" s="4" t="s">
+        <v>43</v>
+      </c>
       <c r="O4" s="4"/>
       <c r="P4" s="4"/>
       <c r="Q4" s="4"/>
@@ -9342,7 +9416,7 @@
       <c r="AA4" s="4"/>
     </row>
     <row r="5" spans="1:27" ht="16.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A5" s="2">
+      <c r="A5" s="56">
         <v>4</v>
       </c>
       <c r="B5" s="4" t="s">
@@ -9354,10 +9428,10 @@
       <c r="D5" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="E5" s="4" t="s">
+      <c r="E5" s="53" t="s">
         <v>40</v>
       </c>
-      <c r="F5" s="4" t="s">
+      <c r="F5" s="53" t="s">
         <v>40</v>
       </c>
       <c r="G5" s="4" t="s">
@@ -9381,7 +9455,9 @@
       <c r="M5" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="N5" s="4"/>
+      <c r="N5" s="4" t="s">
+        <v>41</v>
+      </c>
       <c r="O5" s="4"/>
       <c r="P5" s="4"/>
       <c r="Q5" s="4"/>
@@ -9397,7 +9473,7 @@
       <c r="AA5" s="4"/>
     </row>
     <row r="6" spans="1:27" ht="16.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A6" s="2">
+      <c r="A6" s="56">
         <v>5</v>
       </c>
       <c r="B6" s="4" t="s">
@@ -9409,10 +9485,10 @@
       <c r="D6" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="E6" s="4" t="s">
+      <c r="E6" s="53" t="s">
         <v>40</v>
       </c>
-      <c r="F6" s="4" t="s">
+      <c r="F6" s="53" t="s">
         <v>40</v>
       </c>
       <c r="G6" s="4" t="s">
@@ -9436,7 +9512,9 @@
       <c r="M6" s="4" t="s">
         <v>52</v>
       </c>
-      <c r="N6" s="4"/>
+      <c r="N6" s="4" t="s">
+        <v>44</v>
+      </c>
       <c r="O6" s="4"/>
       <c r="P6" s="4"/>
       <c r="Q6" s="4"/>
@@ -9452,7 +9530,7 @@
       <c r="AA6" s="4"/>
     </row>
     <row r="7" spans="1:27" ht="16.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A7" s="2">
+      <c r="A7" s="56">
         <v>6</v>
       </c>
       <c r="B7" s="4" t="s">
@@ -9464,10 +9542,10 @@
       <c r="D7" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="E7" s="4" t="s">
+      <c r="E7" s="53" t="s">
         <v>40</v>
       </c>
-      <c r="F7" s="4" t="s">
+      <c r="F7" s="53" t="s">
         <v>40</v>
       </c>
       <c r="G7" s="4" t="s">
@@ -9491,7 +9569,9 @@
       <c r="M7" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="N7" s="4"/>
+      <c r="N7" s="4" t="s">
+        <v>46</v>
+      </c>
       <c r="O7" s="4"/>
       <c r="P7" s="4"/>
       <c r="Q7" s="4"/>
@@ -9507,7 +9587,7 @@
       <c r="AA7" s="4"/>
     </row>
     <row r="8" spans="1:27" ht="16.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A8" s="2">
+      <c r="A8" s="56">
         <v>7</v>
       </c>
       <c r="B8" s="4" t="s">
@@ -9519,10 +9599,10 @@
       <c r="D8" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="E8" s="4" t="s">
+      <c r="E8" s="53" t="s">
         <v>40</v>
       </c>
-      <c r="F8" s="4" t="s">
+      <c r="F8" s="53" t="s">
         <v>40</v>
       </c>
       <c r="G8" s="4" t="s">
@@ -9546,7 +9626,9 @@
       <c r="M8" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="N8" s="4"/>
+      <c r="N8" s="4" t="s">
+        <v>42</v>
+      </c>
       <c r="O8" s="4"/>
       <c r="P8" s="4"/>
       <c r="Q8" s="4"/>
@@ -9562,7 +9644,7 @@
       <c r="AA8" s="4"/>
     </row>
     <row r="9" spans="1:27" ht="16.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A9" s="2">
+      <c r="A9" s="56">
         <v>8</v>
       </c>
       <c r="B9" s="4" t="s">
@@ -9574,10 +9656,10 @@
       <c r="D9" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="E9" s="4" t="s">
+      <c r="E9" s="53" t="s">
         <v>40</v>
       </c>
-      <c r="F9" s="4" t="s">
+      <c r="F9" s="53" t="s">
         <v>40</v>
       </c>
       <c r="G9" s="4" t="s">
@@ -9601,7 +9683,9 @@
       <c r="M9" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="N9" s="4"/>
+      <c r="N9" s="4" t="s">
+        <v>47</v>
+      </c>
       <c r="O9" s="4"/>
       <c r="P9" s="4"/>
       <c r="Q9" s="4"/>
@@ -9617,7 +9701,7 @@
       <c r="AA9" s="4"/>
     </row>
     <row r="10" spans="1:27" ht="16.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A10" s="2">
+      <c r="A10" s="56">
         <v>9</v>
       </c>
       <c r="B10" s="4" t="s">
@@ -9629,10 +9713,10 @@
       <c r="D10" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="E10" s="4" t="s">
+      <c r="E10" s="53" t="s">
         <v>40</v>
       </c>
-      <c r="F10" s="4" t="s">
+      <c r="F10" s="53" t="s">
         <v>40</v>
       </c>
       <c r="G10" s="4" t="s">
@@ -9656,7 +9740,9 @@
       <c r="M10" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="N10" s="4"/>
+      <c r="N10" s="4" t="s">
+        <v>62</v>
+      </c>
       <c r="O10" s="4"/>
       <c r="P10" s="4"/>
       <c r="Q10" s="4"/>
@@ -9672,7 +9758,7 @@
       <c r="AA10" s="4"/>
     </row>
     <row r="11" spans="1:27" ht="16.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A11" s="2">
+      <c r="A11" s="56">
         <v>10</v>
       </c>
       <c r="B11" s="4" t="s">
@@ -9684,10 +9770,10 @@
       <c r="D11" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="E11" s="4" t="s">
+      <c r="E11" s="53" t="s">
         <v>40</v>
       </c>
-      <c r="F11" s="4" t="s">
+      <c r="F11" s="53" t="s">
         <v>40</v>
       </c>
       <c r="G11" s="4" t="s">
@@ -9711,7 +9797,9 @@
       <c r="M11" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="N11" s="4"/>
+      <c r="N11" s="4" t="s">
+        <v>48</v>
+      </c>
       <c r="O11" s="4"/>
       <c r="P11" s="4"/>
       <c r="Q11" s="4"/>
@@ -9727,7 +9815,7 @@
       <c r="AA11" s="4"/>
     </row>
     <row r="12" spans="1:27" ht="16.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A12" s="2">
+      <c r="A12" s="56">
         <v>11</v>
       </c>
       <c r="B12" s="4" t="s">
@@ -9739,10 +9827,10 @@
       <c r="D12" s="4" t="s">
         <v>62</v>
       </c>
-      <c r="E12" s="4" t="s">
+      <c r="E12" s="53" t="s">
         <v>40</v>
       </c>
-      <c r="F12" s="4" t="s">
+      <c r="F12" s="53" t="s">
         <v>40</v>
       </c>
       <c r="G12" s="4" t="s">
@@ -9766,7 +9854,9 @@
       <c r="M12" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="N12" s="4"/>
+      <c r="N12" s="4" t="s">
+        <v>49</v>
+      </c>
       <c r="O12" s="4"/>
       <c r="P12" s="4"/>
       <c r="Q12" s="4"/>
@@ -9782,7 +9872,7 @@
       <c r="AA12" s="4"/>
     </row>
     <row r="13" spans="1:27" ht="16.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A13" s="2">
+      <c r="A13" s="56">
         <v>12</v>
       </c>
       <c r="B13" s="4" t="s">
@@ -9794,10 +9884,10 @@
       <c r="D13" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="E13" s="4" t="s">
+      <c r="E13" s="53" t="s">
         <v>40</v>
       </c>
-      <c r="F13" s="4" t="s">
+      <c r="F13" s="53" t="s">
         <v>40</v>
       </c>
       <c r="G13" s="4" t="s">
@@ -9821,7 +9911,9 @@
       <c r="M13" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="N13" s="4"/>
+      <c r="N13" s="4" t="s">
+        <v>51</v>
+      </c>
       <c r="O13" s="4"/>
       <c r="P13" s="4"/>
       <c r="Q13" s="4"/>
@@ -9837,7 +9929,7 @@
       <c r="AA13" s="4"/>
     </row>
     <row r="14" spans="1:27" ht="16.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A14" s="2">
+      <c r="A14" s="56">
         <v>13</v>
       </c>
       <c r="B14" s="4" t="s">
@@ -9849,10 +9941,10 @@
       <c r="D14" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="E14" s="4" t="s">
+      <c r="E14" s="53" t="s">
         <v>40</v>
       </c>
-      <c r="F14" s="4" t="s">
+      <c r="F14" s="53" t="s">
         <v>40</v>
       </c>
       <c r="G14" s="4" t="s">
@@ -9876,7 +9968,9 @@
       <c r="M14" s="4" t="s">
         <v>62</v>
       </c>
-      <c r="N14" s="4"/>
+      <c r="N14" s="4" t="s">
+        <v>59</v>
+      </c>
       <c r="O14" s="4"/>
       <c r="P14" s="4"/>
       <c r="Q14" s="4"/>
@@ -9892,7 +9986,7 @@
       <c r="AA14" s="4"/>
     </row>
     <row r="15" spans="1:27" ht="16.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A15" s="2">
+      <c r="A15" s="56">
         <v>14</v>
       </c>
       <c r="B15" s="4" t="s">
@@ -9904,10 +9998,10 @@
       <c r="D15" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="E15" s="4" t="s">
+      <c r="E15" s="53" t="s">
         <v>40</v>
       </c>
-      <c r="F15" s="4" t="s">
+      <c r="F15" s="53" t="s">
         <v>40</v>
       </c>
       <c r="G15" s="4" t="s">
@@ -9931,7 +10025,9 @@
       <c r="M15" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="N15" s="4"/>
+      <c r="N15" s="4" t="s">
+        <v>58</v>
+      </c>
       <c r="O15" s="4"/>
       <c r="P15" s="4"/>
       <c r="Q15" s="4"/>
@@ -9947,7 +10043,7 @@
       <c r="AA15" s="4"/>
     </row>
     <row r="16" spans="1:27" ht="16.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A16" s="2">
+      <c r="A16" s="56">
         <v>15</v>
       </c>
       <c r="B16" s="4" t="s">
@@ -9959,10 +10055,10 @@
       <c r="D16" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="E16" s="4" t="s">
+      <c r="E16" s="53" t="s">
         <v>40</v>
       </c>
-      <c r="F16" s="4" t="s">
+      <c r="F16" s="53" t="s">
         <v>40</v>
       </c>
       <c r="G16" s="4" t="s">
@@ -9986,7 +10082,9 @@
       <c r="M16" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="N16" s="4"/>
+      <c r="N16" s="4" t="s">
+        <v>50</v>
+      </c>
       <c r="O16" s="4"/>
       <c r="P16" s="4"/>
       <c r="Q16" s="4"/>
@@ -10002,7 +10100,7 @@
       <c r="AA16" s="4"/>
     </row>
     <row r="17" spans="1:27" ht="16.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A17" s="2">
+      <c r="A17" s="56">
         <v>16</v>
       </c>
       <c r="B17" s="4" t="s">
@@ -10014,10 +10112,10 @@
       <c r="D17" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="E17" s="4" t="s">
+      <c r="E17" s="53" t="s">
         <v>40</v>
       </c>
-      <c r="F17" s="4" t="s">
+      <c r="F17" s="53" t="s">
         <v>40</v>
       </c>
       <c r="G17" s="4" t="s">
@@ -10041,7 +10139,9 @@
       <c r="M17" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="N17" s="4"/>
+      <c r="N17" s="4" t="s">
+        <v>54</v>
+      </c>
       <c r="O17" s="4"/>
       <c r="P17" s="4"/>
       <c r="Q17" s="4"/>
@@ -10057,7 +10157,7 @@
       <c r="AA17" s="4"/>
     </row>
     <row r="18" spans="1:27" ht="16.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A18" s="2">
+      <c r="A18" s="56">
         <v>17</v>
       </c>
       <c r="B18" s="4" t="s">
@@ -10069,10 +10169,10 @@
       <c r="D18" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="E18" s="4" t="s">
+      <c r="E18" s="53" t="s">
         <v>40</v>
       </c>
-      <c r="F18" s="4" t="s">
+      <c r="F18" s="53" t="s">
         <v>40</v>
       </c>
       <c r="G18" s="4" t="s">
@@ -10096,7 +10196,9 @@
       <c r="M18" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="N18" s="4"/>
+      <c r="N18" s="4" t="s">
+        <v>61</v>
+      </c>
       <c r="O18" s="4"/>
       <c r="P18" s="4"/>
       <c r="Q18" s="4"/>
@@ -10112,7 +10214,7 @@
       <c r="AA18" s="4"/>
     </row>
     <row r="19" spans="1:27" ht="16.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A19" s="2">
+      <c r="A19" s="56">
         <v>18</v>
       </c>
       <c r="B19" s="4" t="s">
@@ -10124,10 +10226,10 @@
       <c r="D19" s="4" t="s">
         <v>58</v>
       </c>
-      <c r="E19" s="4" t="s">
+      <c r="E19" s="53" t="s">
         <v>40</v>
       </c>
-      <c r="F19" s="4" t="s">
+      <c r="F19" s="53" t="s">
         <v>40</v>
       </c>
       <c r="G19" s="4" t="s">
@@ -10151,7 +10253,9 @@
       <c r="M19" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="N19" s="4"/>
+      <c r="N19" s="4" t="s">
+        <v>57</v>
+      </c>
       <c r="O19" s="4"/>
       <c r="P19" s="4"/>
       <c r="Q19" s="4"/>
@@ -10167,7 +10271,7 @@
       <c r="AA19" s="4"/>
     </row>
     <row r="20" spans="1:27" ht="16.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A20" s="2">
+      <c r="A20" s="56">
         <v>19</v>
       </c>
       <c r="B20" s="4" t="s">
@@ -10179,10 +10283,10 @@
       <c r="D20" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="E20" s="4" t="s">
+      <c r="E20" s="53" t="s">
         <v>40</v>
       </c>
-      <c r="F20" s="4" t="s">
+      <c r="F20" s="53" t="s">
         <v>40</v>
       </c>
       <c r="G20" s="4" t="s">
@@ -10206,7 +10310,9 @@
       <c r="M20" s="4" t="s">
         <v>58</v>
       </c>
-      <c r="N20" s="4"/>
+      <c r="N20" s="4" t="s">
+        <v>53</v>
+      </c>
       <c r="O20" s="4"/>
       <c r="P20" s="4"/>
       <c r="Q20" s="4"/>
@@ -10222,7 +10328,7 @@
       <c r="AA20" s="4"/>
     </row>
     <row r="21" spans="1:27" ht="16.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A21" s="2">
+      <c r="A21" s="56">
         <v>20</v>
       </c>
       <c r="B21" s="4" t="s">
@@ -10234,10 +10340,10 @@
       <c r="D21" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="E21" s="4" t="s">
+      <c r="E21" s="53" t="s">
         <v>40</v>
       </c>
-      <c r="F21" s="4" t="s">
+      <c r="F21" s="53" t="s">
         <v>40</v>
       </c>
       <c r="G21" s="4" t="s">
@@ -10261,7 +10367,9 @@
       <c r="M21" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="N21" s="4"/>
+      <c r="N21" s="4" t="s">
+        <v>52</v>
+      </c>
       <c r="O21" s="4"/>
       <c r="P21" s="4"/>
       <c r="Q21" s="4"/>
@@ -10277,7 +10385,7 @@
       <c r="AA21" s="4"/>
     </row>
     <row r="22" spans="1:27" ht="16.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A22" s="2">
+      <c r="A22" s="56">
         <v>21</v>
       </c>
       <c r="B22" s="4" t="s">
@@ -10289,10 +10397,10 @@
       <c r="D22" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="E22" s="4" t="s">
+      <c r="E22" s="53" t="s">
         <v>40</v>
       </c>
-      <c r="F22" s="4" t="s">
+      <c r="F22" s="53" t="s">
         <v>40</v>
       </c>
       <c r="G22" s="4" t="s">
@@ -10316,7 +10424,9 @@
       <c r="M22" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="N22" s="4"/>
+      <c r="N22" s="4" t="s">
+        <v>55</v>
+      </c>
       <c r="O22" s="4"/>
       <c r="P22" s="4"/>
       <c r="Q22" s="4"/>
@@ -10332,7 +10442,7 @@
       <c r="AA22" s="4"/>
     </row>
     <row r="23" spans="1:27" ht="16.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A23" s="2">
+      <c r="A23" s="56">
         <v>22</v>
       </c>
       <c r="B23" s="4" t="s">
@@ -10344,10 +10454,10 @@
       <c r="D23" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="E23" s="4" t="s">
+      <c r="E23" s="53" t="s">
         <v>40</v>
       </c>
-      <c r="F23" s="4" t="s">
+      <c r="F23" s="53" t="s">
         <v>40</v>
       </c>
       <c r="G23" s="4" t="s">
@@ -10371,7 +10481,9 @@
       <c r="M23" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="N23" s="4"/>
+      <c r="N23" s="4" t="s">
+        <v>56</v>
+      </c>
       <c r="O23" s="4"/>
       <c r="P23" s="4"/>
       <c r="Q23" s="4"/>
@@ -10581,27 +10693,27 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="21.6" x14ac:dyDescent="0.4">
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="56" t="s">
         <v>17</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="56" t="s">
         <v>21</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="56" t="s">
         <v>22</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="56" t="s">
         <v>26</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="56" t="s">
         <v>29</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="G1" s="56" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="2" spans="1:7" ht="21.6" x14ac:dyDescent="0.4">
-      <c r="A2" s="2">
+      <c r="A2" s="54">
         <v>1</v>
       </c>
       <c r="B2" s="4" t="s">
@@ -10620,7 +10732,7 @@
       <c r="G2" s="4"/>
     </row>
     <row r="3" spans="1:7" ht="21.6" x14ac:dyDescent="0.4">
-      <c r="A3" s="2">
+      <c r="A3" s="17">
         <v>2</v>
       </c>
       <c r="B3" s="4" t="s">
@@ -10639,7 +10751,7 @@
       <c r="G3" s="4"/>
     </row>
     <row r="4" spans="1:7" ht="21.6" x14ac:dyDescent="0.4">
-      <c r="A4" s="2">
+      <c r="A4" s="55">
         <v>3</v>
       </c>
       <c r="B4" s="4" t="s">
@@ -10658,7 +10770,7 @@
       <c r="G4" s="4"/>
     </row>
     <row r="5" spans="1:7" ht="21.6" x14ac:dyDescent="0.4">
-      <c r="A5" s="2">
+      <c r="A5" s="56">
         <v>4</v>
       </c>
       <c r="B5" s="4" t="s">
@@ -10677,7 +10789,7 @@
       <c r="G5" s="4"/>
     </row>
     <row r="6" spans="1:7" ht="21.6" x14ac:dyDescent="0.4">
-      <c r="A6" s="2">
+      <c r="A6" s="56">
         <v>5</v>
       </c>
       <c r="B6" s="4" t="s">
@@ -10696,7 +10808,7 @@
       <c r="G6" s="4"/>
     </row>
     <row r="7" spans="1:7" ht="21.6" x14ac:dyDescent="0.4">
-      <c r="A7" s="2">
+      <c r="A7" s="56">
         <v>6</v>
       </c>
       <c r="B7" s="4" t="s">
@@ -10715,7 +10827,7 @@
       <c r="G7" s="4"/>
     </row>
     <row r="8" spans="1:7" ht="21.6" x14ac:dyDescent="0.4">
-      <c r="A8" s="2">
+      <c r="A8" s="56">
         <v>7</v>
       </c>
       <c r="B8" s="4" t="s">
@@ -10734,7 +10846,7 @@
       <c r="G8" s="4"/>
     </row>
     <row r="9" spans="1:7" ht="21.6" x14ac:dyDescent="0.4">
-      <c r="A9" s="2">
+      <c r="A9" s="56">
         <v>8</v>
       </c>
       <c r="B9" s="4" t="s">
@@ -10753,7 +10865,7 @@
       <c r="G9" s="4"/>
     </row>
     <row r="10" spans="1:7" ht="21.6" x14ac:dyDescent="0.4">
-      <c r="A10" s="2">
+      <c r="A10" s="56">
         <v>9</v>
       </c>
       <c r="B10" s="4" t="s">
@@ -10772,7 +10884,7 @@
       <c r="G10" s="4"/>
     </row>
     <row r="11" spans="1:7" ht="21.6" x14ac:dyDescent="0.4">
-      <c r="A11" s="2">
+      <c r="A11" s="56">
         <v>10</v>
       </c>
       <c r="B11" s="4" t="s">
@@ -10791,7 +10903,7 @@
       <c r="G11" s="4"/>
     </row>
     <row r="12" spans="1:7" ht="21.6" x14ac:dyDescent="0.4">
-      <c r="A12" s="2">
+      <c r="A12" s="56">
         <v>11</v>
       </c>
       <c r="B12" s="4" t="s">
@@ -10810,7 +10922,7 @@
       <c r="G12" s="4"/>
     </row>
     <row r="13" spans="1:7" ht="21.6" x14ac:dyDescent="0.4">
-      <c r="A13" s="2">
+      <c r="A13" s="56">
         <v>12</v>
       </c>
       <c r="B13" s="4" t="s">
@@ -10829,7 +10941,7 @@
       <c r="G13" s="4"/>
     </row>
     <row r="14" spans="1:7" ht="21.6" x14ac:dyDescent="0.4">
-      <c r="A14" s="2">
+      <c r="A14" s="56">
         <v>13</v>
       </c>
       <c r="B14" s="4" t="s">
@@ -10848,7 +10960,7 @@
       <c r="G14" s="4"/>
     </row>
     <row r="15" spans="1:7" ht="21.6" x14ac:dyDescent="0.4">
-      <c r="A15" s="2">
+      <c r="A15" s="56">
         <v>14</v>
       </c>
       <c r="B15" s="4" t="s">
@@ -10867,7 +10979,7 @@
       <c r="G15" s="4"/>
     </row>
     <row r="16" spans="1:7" ht="21.6" x14ac:dyDescent="0.4">
-      <c r="A16" s="2">
+      <c r="A16" s="56">
         <v>15</v>
       </c>
       <c r="B16" s="4" t="s">
@@ -10886,7 +10998,7 @@
       <c r="G16" s="4"/>
     </row>
     <row r="17" spans="1:7" ht="21.6" x14ac:dyDescent="0.4">
-      <c r="A17" s="2">
+      <c r="A17" s="56">
         <v>16</v>
       </c>
       <c r="B17" s="4" t="s">
@@ -10905,7 +11017,7 @@
       <c r="G17" s="4"/>
     </row>
     <row r="18" spans="1:7" ht="21.6" x14ac:dyDescent="0.4">
-      <c r="A18" s="2">
+      <c r="A18" s="56">
         <v>17</v>
       </c>
       <c r="B18" s="4" t="s">
@@ -10924,7 +11036,7 @@
       <c r="G18" s="4"/>
     </row>
     <row r="19" spans="1:7" ht="21.6" x14ac:dyDescent="0.4">
-      <c r="A19" s="2">
+      <c r="A19" s="56">
         <v>18</v>
       </c>
       <c r="B19" s="4" t="s">
@@ -10943,7 +11055,7 @@
       <c r="G19" s="4"/>
     </row>
     <row r="20" spans="1:7" ht="21.6" x14ac:dyDescent="0.4">
-      <c r="A20" s="2">
+      <c r="A20" s="56">
         <v>19</v>
       </c>
       <c r="B20" s="4" t="s">
@@ -10962,7 +11074,7 @@
       <c r="G20" s="4"/>
     </row>
     <row r="21" spans="1:7" ht="21.6" x14ac:dyDescent="0.4">
-      <c r="A21" s="2">
+      <c r="A21" s="56">
         <v>20</v>
       </c>
       <c r="B21" s="4" t="s">
@@ -10981,7 +11093,7 @@
       <c r="G21" s="4"/>
     </row>
     <row r="22" spans="1:7" ht="21.6" x14ac:dyDescent="0.4">
-      <c r="A22" s="2">
+      <c r="A22" s="56">
         <v>21</v>
       </c>
       <c r="B22" s="4" t="s">
@@ -11000,7 +11112,7 @@
       <c r="G22" s="4"/>
     </row>
     <row r="23" spans="1:7" ht="21.6" x14ac:dyDescent="0.4">
-      <c r="A23" s="2">
+      <c r="A23" s="56">
         <v>22</v>
       </c>
       <c r="B23" s="4" t="s">
@@ -11193,51 +11305,51 @@
       </c>
       <c r="N2">
         <f>M2+'Drivers'' Standings'!O2</f>
-        <v>204</v>
+        <v>219</v>
       </c>
       <c r="O2">
         <f>N2+'Drivers'' Standings'!P2</f>
-        <v>204</v>
+        <v>219</v>
       </c>
       <c r="P2">
         <f>O2+'Drivers'' Standings'!Q2</f>
-        <v>204</v>
+        <v>219</v>
       </c>
       <c r="Q2">
         <f>P2+'Drivers'' Standings'!R2</f>
-        <v>204</v>
+        <v>219</v>
       </c>
       <c r="R2">
         <f>Q2+'Drivers'' Standings'!S2</f>
-        <v>204</v>
+        <v>219</v>
       </c>
       <c r="S2">
         <f>R2+'Drivers'' Standings'!T2</f>
-        <v>204</v>
+        <v>219</v>
       </c>
       <c r="T2">
         <f>S2+'Drivers'' Standings'!U2</f>
-        <v>204</v>
+        <v>219</v>
       </c>
       <c r="U2">
         <f>T2+'Drivers'' Standings'!V2</f>
-        <v>204</v>
+        <v>219</v>
       </c>
       <c r="V2">
         <f>U2+'Drivers'' Standings'!W2</f>
-        <v>204</v>
+        <v>219</v>
       </c>
       <c r="W2">
         <f>V2+'Drivers'' Standings'!X2</f>
-        <v>204</v>
+        <v>219</v>
       </c>
       <c r="X2">
         <f>W2+'Drivers'' Standings'!Y2</f>
-        <v>204</v>
+        <v>219</v>
       </c>
       <c r="Y2">
         <f>X2+'Drivers'' Standings'!Z2</f>
-        <v>204</v>
+        <v>219</v>
       </c>
       <c r="AB2" t="s">
         <v>73</v>
@@ -11249,7 +11361,7 @@
         <v>76</v>
       </c>
       <c r="AE2" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="AF2" t="s">
         <v>64</v>
@@ -11260,7 +11372,7 @@
       </c>
       <c r="BC2" s="44">
         <f>Y2</f>
-        <v>204</v>
+        <v>219</v>
       </c>
       <c r="BD2" s="44">
         <f>MAX($BC$2:$BC$23)-BC2</f>
@@ -11321,51 +11433,51 @@
       </c>
       <c r="N3">
         <f>M3+'Drivers'' Standings'!O3</f>
-        <v>154</v>
+        <v>160</v>
       </c>
       <c r="O3">
         <f>N3+'Drivers'' Standings'!P3</f>
-        <v>154</v>
+        <v>160</v>
       </c>
       <c r="P3">
         <f>O3+'Drivers'' Standings'!Q3</f>
-        <v>154</v>
+        <v>160</v>
       </c>
       <c r="Q3">
         <f>P3+'Drivers'' Standings'!R3</f>
-        <v>154</v>
+        <v>160</v>
       </c>
       <c r="R3">
         <f>Q3+'Drivers'' Standings'!S3</f>
-        <v>154</v>
+        <v>160</v>
       </c>
       <c r="S3">
         <f>R3+'Drivers'' Standings'!T3</f>
-        <v>154</v>
+        <v>160</v>
       </c>
       <c r="T3">
         <f>S3+'Drivers'' Standings'!U3</f>
-        <v>154</v>
+        <v>160</v>
       </c>
       <c r="U3">
         <f>T3+'Drivers'' Standings'!V3</f>
-        <v>154</v>
+        <v>160</v>
       </c>
       <c r="V3">
         <f>U3+'Drivers'' Standings'!W3</f>
-        <v>154</v>
+        <v>160</v>
       </c>
       <c r="W3">
         <f>V3+'Drivers'' Standings'!X3</f>
-        <v>154</v>
+        <v>160</v>
       </c>
       <c r="X3">
         <f>W3+'Drivers'' Standings'!Y3</f>
-        <v>154</v>
+        <v>160</v>
       </c>
       <c r="Y3">
         <f>X3+'Drivers'' Standings'!Z3</f>
-        <v>154</v>
+        <v>160</v>
       </c>
       <c r="BB3" s="44" t="str">
         <f t="shared" si="0"/>
@@ -11373,11 +11485,11 @@
       </c>
       <c r="BC3" s="44">
         <f t="shared" ref="BC3:BC23" si="1">Y3</f>
-        <v>154</v>
+        <v>160</v>
       </c>
       <c r="BD3" s="44">
         <f t="shared" ref="BD3:BD23" si="2">MAX($BC$2:$BC$23)-BC3</f>
-        <v>50</v>
+        <v>59</v>
       </c>
     </row>
     <row r="4" spans="1:56" ht="21.6" x14ac:dyDescent="0.4">
@@ -11434,51 +11546,51 @@
       </c>
       <c r="N4">
         <f>M4+'Drivers'' Standings'!O4</f>
-        <v>159</v>
+        <v>169</v>
       </c>
       <c r="O4">
         <f>N4+'Drivers'' Standings'!P4</f>
-        <v>159</v>
+        <v>169</v>
       </c>
       <c r="P4">
         <f>O4+'Drivers'' Standings'!Q4</f>
-        <v>159</v>
+        <v>169</v>
       </c>
       <c r="Q4">
         <f>P4+'Drivers'' Standings'!R4</f>
-        <v>159</v>
+        <v>169</v>
       </c>
       <c r="R4">
         <f>Q4+'Drivers'' Standings'!S4</f>
-        <v>159</v>
+        <v>169</v>
       </c>
       <c r="S4">
         <f>R4+'Drivers'' Standings'!T4</f>
-        <v>159</v>
+        <v>169</v>
       </c>
       <c r="T4">
         <f>S4+'Drivers'' Standings'!U4</f>
-        <v>159</v>
+        <v>169</v>
       </c>
       <c r="U4">
         <f>T4+'Drivers'' Standings'!V4</f>
-        <v>159</v>
+        <v>169</v>
       </c>
       <c r="V4">
         <f>U4+'Drivers'' Standings'!W4</f>
-        <v>159</v>
+        <v>169</v>
       </c>
       <c r="W4">
         <f>V4+'Drivers'' Standings'!X4</f>
-        <v>159</v>
+        <v>169</v>
       </c>
       <c r="X4">
         <f>W4+'Drivers'' Standings'!Y4</f>
-        <v>159</v>
+        <v>169</v>
       </c>
       <c r="Y4">
         <f>X4+'Drivers'' Standings'!Z4</f>
-        <v>159</v>
+        <v>169</v>
       </c>
       <c r="AC4" s="2" t="s">
         <v>16</v>
@@ -11558,11 +11670,11 @@
       </c>
       <c r="BC4" s="44">
         <f t="shared" si="1"/>
-        <v>159</v>
+        <v>169</v>
       </c>
       <c r="BD4" s="44">
         <f t="shared" si="2"/>
-        <v>45</v>
+        <v>50</v>
       </c>
     </row>
     <row r="5" spans="1:56" ht="21.6" x14ac:dyDescent="0.4">
@@ -11619,51 +11731,51 @@
       </c>
       <c r="N5">
         <f>M5+'Drivers'' Standings'!O5</f>
-        <v>126</v>
+        <v>138</v>
       </c>
       <c r="O5">
         <f>N5+'Drivers'' Standings'!P5</f>
-        <v>126</v>
+        <v>138</v>
       </c>
       <c r="P5">
         <f>O5+'Drivers'' Standings'!Q5</f>
-        <v>126</v>
+        <v>138</v>
       </c>
       <c r="Q5">
         <f>P5+'Drivers'' Standings'!R5</f>
-        <v>126</v>
+        <v>138</v>
       </c>
       <c r="R5">
         <f>Q5+'Drivers'' Standings'!S5</f>
-        <v>126</v>
+        <v>138</v>
       </c>
       <c r="S5">
         <f>R5+'Drivers'' Standings'!T5</f>
-        <v>126</v>
+        <v>138</v>
       </c>
       <c r="T5">
         <f>S5+'Drivers'' Standings'!U5</f>
-        <v>126</v>
+        <v>138</v>
       </c>
       <c r="U5">
         <f>T5+'Drivers'' Standings'!V5</f>
-        <v>126</v>
+        <v>138</v>
       </c>
       <c r="V5">
         <f>U5+'Drivers'' Standings'!W5</f>
-        <v>126</v>
+        <v>138</v>
       </c>
       <c r="W5">
         <f>V5+'Drivers'' Standings'!X5</f>
-        <v>126</v>
+        <v>138</v>
       </c>
       <c r="X5">
         <f>W5+'Drivers'' Standings'!Y5</f>
-        <v>126</v>
+        <v>138</v>
       </c>
       <c r="Y5">
         <f>X5+'Drivers'' Standings'!Z5</f>
-        <v>126</v>
+        <v>138</v>
       </c>
       <c r="AB5" t="str">
         <f>AB2</f>
@@ -11719,51 +11831,51 @@
       </c>
       <c r="AO5">
         <f t="shared" si="3"/>
-        <v>154</v>
+        <v>160</v>
       </c>
       <c r="AP5">
         <f t="shared" si="3"/>
-        <v>154</v>
+        <v>160</v>
       </c>
       <c r="AQ5">
         <f t="shared" si="3"/>
-        <v>154</v>
+        <v>160</v>
       </c>
       <c r="AR5">
         <f t="shared" si="3"/>
-        <v>154</v>
+        <v>160</v>
       </c>
       <c r="AS5">
         <f t="shared" si="3"/>
-        <v>154</v>
+        <v>160</v>
       </c>
       <c r="AT5">
         <f t="shared" si="3"/>
-        <v>154</v>
+        <v>160</v>
       </c>
       <c r="AU5">
         <f t="shared" si="3"/>
-        <v>154</v>
+        <v>160</v>
       </c>
       <c r="AV5">
         <f t="shared" si="3"/>
-        <v>154</v>
+        <v>160</v>
       </c>
       <c r="AW5">
         <f t="shared" si="3"/>
-        <v>154</v>
+        <v>160</v>
       </c>
       <c r="AX5">
         <f t="shared" si="3"/>
-        <v>154</v>
+        <v>160</v>
       </c>
       <c r="AY5">
         <f t="shared" si="3"/>
-        <v>154</v>
+        <v>160</v>
       </c>
       <c r="AZ5">
         <f t="shared" si="3"/>
-        <v>154</v>
+        <v>160</v>
       </c>
       <c r="BB5" s="44" t="str">
         <f t="shared" si="0"/>
@@ -11771,11 +11883,11 @@
       </c>
       <c r="BC5" s="44">
         <f t="shared" si="1"/>
-        <v>126</v>
+        <v>138</v>
       </c>
       <c r="BD5" s="44">
         <f t="shared" si="2"/>
-        <v>78</v>
+        <v>81</v>
       </c>
     </row>
     <row r="6" spans="1:56" ht="21.6" x14ac:dyDescent="0.4">
@@ -11832,51 +11944,51 @@
       </c>
       <c r="N6">
         <f>M6+'Drivers'' Standings'!O6</f>
-        <v>103</v>
+        <v>128</v>
       </c>
       <c r="O6">
         <f>N6+'Drivers'' Standings'!P6</f>
-        <v>103</v>
+        <v>128</v>
       </c>
       <c r="P6">
         <f>O6+'Drivers'' Standings'!Q6</f>
-        <v>103</v>
+        <v>128</v>
       </c>
       <c r="Q6">
         <f>P6+'Drivers'' Standings'!R6</f>
-        <v>103</v>
+        <v>128</v>
       </c>
       <c r="R6">
         <f>Q6+'Drivers'' Standings'!S6</f>
-        <v>103</v>
+        <v>128</v>
       </c>
       <c r="S6">
         <f>R6+'Drivers'' Standings'!T6</f>
-        <v>103</v>
+        <v>128</v>
       </c>
       <c r="T6">
         <f>S6+'Drivers'' Standings'!U6</f>
-        <v>103</v>
+        <v>128</v>
       </c>
       <c r="U6">
         <f>T6+'Drivers'' Standings'!V6</f>
-        <v>103</v>
+        <v>128</v>
       </c>
       <c r="V6">
         <f>U6+'Drivers'' Standings'!W6</f>
-        <v>103</v>
+        <v>128</v>
       </c>
       <c r="W6">
         <f>V6+'Drivers'' Standings'!X6</f>
-        <v>103</v>
+        <v>128</v>
       </c>
       <c r="X6">
         <f>W6+'Drivers'' Standings'!Y6</f>
-        <v>103</v>
+        <v>128</v>
       </c>
       <c r="Y6">
         <f>X6+'Drivers'' Standings'!Z6</f>
-        <v>103</v>
+        <v>128</v>
       </c>
       <c r="AB6" t="str">
         <f>AC2</f>
@@ -11932,51 +12044,51 @@
       </c>
       <c r="AO6">
         <f t="shared" si="3"/>
-        <v>159</v>
+        <v>169</v>
       </c>
       <c r="AP6">
         <f t="shared" si="3"/>
-        <v>159</v>
+        <v>169</v>
       </c>
       <c r="AQ6">
         <f t="shared" si="3"/>
-        <v>159</v>
+        <v>169</v>
       </c>
       <c r="AR6">
         <f t="shared" si="3"/>
-        <v>159</v>
+        <v>169</v>
       </c>
       <c r="AS6">
         <f t="shared" si="3"/>
-        <v>159</v>
+        <v>169</v>
       </c>
       <c r="AT6">
         <f t="shared" si="3"/>
-        <v>159</v>
+        <v>169</v>
       </c>
       <c r="AU6">
         <f t="shared" si="3"/>
-        <v>159</v>
+        <v>169</v>
       </c>
       <c r="AV6">
         <f t="shared" si="3"/>
-        <v>159</v>
+        <v>169</v>
       </c>
       <c r="AW6">
         <f t="shared" si="3"/>
-        <v>159</v>
+        <v>169</v>
       </c>
       <c r="AX6">
         <f t="shared" si="3"/>
-        <v>159</v>
+        <v>169</v>
       </c>
       <c r="AY6">
         <f t="shared" si="3"/>
-        <v>159</v>
+        <v>169</v>
       </c>
       <c r="AZ6">
         <f t="shared" si="3"/>
-        <v>159</v>
+        <v>169</v>
       </c>
       <c r="BB6" s="44" t="str">
         <f t="shared" si="0"/>
@@ -11984,11 +12096,11 @@
       </c>
       <c r="BC6" s="44">
         <f t="shared" si="1"/>
-        <v>103</v>
+        <v>128</v>
       </c>
       <c r="BD6" s="44">
         <f t="shared" si="2"/>
-        <v>101</v>
+        <v>91</v>
       </c>
     </row>
     <row r="7" spans="1:56" ht="21.6" x14ac:dyDescent="0.4">
@@ -12145,51 +12257,51 @@
       </c>
       <c r="AO7">
         <f t="shared" si="3"/>
-        <v>126</v>
+        <v>138</v>
       </c>
       <c r="AP7">
         <f t="shared" si="3"/>
-        <v>126</v>
+        <v>138</v>
       </c>
       <c r="AQ7">
         <f t="shared" si="3"/>
-        <v>126</v>
+        <v>138</v>
       </c>
       <c r="AR7">
         <f t="shared" si="3"/>
-        <v>126</v>
+        <v>138</v>
       </c>
       <c r="AS7">
         <f t="shared" si="3"/>
-        <v>126</v>
+        <v>138</v>
       </c>
       <c r="AT7">
         <f t="shared" si="3"/>
-        <v>126</v>
+        <v>138</v>
       </c>
       <c r="AU7">
         <f t="shared" si="3"/>
-        <v>126</v>
+        <v>138</v>
       </c>
       <c r="AV7">
         <f t="shared" si="3"/>
-        <v>126</v>
+        <v>138</v>
       </c>
       <c r="AW7">
         <f t="shared" si="3"/>
-        <v>126</v>
+        <v>138</v>
       </c>
       <c r="AX7">
         <f t="shared" si="3"/>
-        <v>126</v>
+        <v>138</v>
       </c>
       <c r="AY7">
         <f t="shared" si="3"/>
-        <v>126</v>
+        <v>138</v>
       </c>
       <c r="AZ7">
         <f t="shared" si="3"/>
-        <v>126</v>
+        <v>138</v>
       </c>
       <c r="BB7" s="44" t="str">
         <f t="shared" si="0"/>
@@ -12201,7 +12313,7 @@
       </c>
       <c r="BD7" s="44">
         <f t="shared" si="2"/>
-        <v>112</v>
+        <v>127</v>
       </c>
     </row>
     <row r="8" spans="1:56" ht="21.6" x14ac:dyDescent="0.4">
@@ -12258,151 +12370,151 @@
       </c>
       <c r="N8">
         <f>M8+'Drivers'' Standings'!O8</f>
-        <v>91</v>
+        <v>109</v>
       </c>
       <c r="O8">
         <f>N8+'Drivers'' Standings'!P8</f>
-        <v>91</v>
+        <v>109</v>
       </c>
       <c r="P8">
         <f>O8+'Drivers'' Standings'!Q8</f>
-        <v>91</v>
+        <v>109</v>
       </c>
       <c r="Q8">
         <f>P8+'Drivers'' Standings'!R8</f>
-        <v>91</v>
+        <v>109</v>
       </c>
       <c r="R8">
         <f>Q8+'Drivers'' Standings'!S8</f>
-        <v>91</v>
+        <v>109</v>
       </c>
       <c r="S8">
         <f>R8+'Drivers'' Standings'!T8</f>
-        <v>91</v>
+        <v>109</v>
       </c>
       <c r="T8">
         <f>S8+'Drivers'' Standings'!U8</f>
-        <v>91</v>
+        <v>109</v>
       </c>
       <c r="U8">
         <f>T8+'Drivers'' Standings'!V8</f>
-        <v>91</v>
+        <v>109</v>
       </c>
       <c r="V8">
         <f>U8+'Drivers'' Standings'!W8</f>
-        <v>91</v>
+        <v>109</v>
       </c>
       <c r="W8">
         <f>V8+'Drivers'' Standings'!X8</f>
-        <v>91</v>
+        <v>109</v>
       </c>
       <c r="X8">
         <f>W8+'Drivers'' Standings'!Y8</f>
-        <v>91</v>
+        <v>109</v>
       </c>
       <c r="Y8">
         <f>X8+'Drivers'' Standings'!Z8</f>
-        <v>91</v>
+        <v>109</v>
       </c>
       <c r="AB8" t="str">
         <f>AE2</f>
-        <v>Max Verstappen</v>
+        <v>Lando Norris</v>
       </c>
       <c r="AC8">
         <f t="shared" si="4"/>
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AD8">
         <f t="shared" si="3"/>
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="AE8">
         <f t="shared" si="3"/>
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="AF8">
         <f t="shared" si="3"/>
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="AG8">
         <f t="shared" si="3"/>
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="AH8">
         <f t="shared" si="3"/>
-        <v>26</v>
+        <v>51</v>
       </c>
       <c r="AI8">
         <f t="shared" si="3"/>
-        <v>43</v>
+        <v>58</v>
       </c>
       <c r="AJ8">
         <f t="shared" si="3"/>
-        <v>43</v>
+        <v>58</v>
       </c>
       <c r="AK8">
         <f t="shared" si="3"/>
-        <v>55</v>
+        <v>73</v>
       </c>
       <c r="AL8">
         <f t="shared" si="3"/>
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="AM8">
         <f t="shared" si="3"/>
-        <v>76</v>
+        <v>97</v>
       </c>
       <c r="AN8">
         <f t="shared" si="3"/>
-        <v>91</v>
+        <v>103</v>
       </c>
       <c r="AO8">
         <f t="shared" si="3"/>
-        <v>91</v>
+        <v>128</v>
       </c>
       <c r="AP8">
         <f t="shared" si="3"/>
-        <v>91</v>
+        <v>128</v>
       </c>
       <c r="AQ8">
         <f t="shared" si="3"/>
-        <v>91</v>
+        <v>128</v>
       </c>
       <c r="AR8">
         <f t="shared" si="3"/>
-        <v>91</v>
+        <v>128</v>
       </c>
       <c r="AS8">
         <f t="shared" si="3"/>
-        <v>91</v>
+        <v>128</v>
       </c>
       <c r="AT8">
         <f t="shared" si="3"/>
-        <v>91</v>
+        <v>128</v>
       </c>
       <c r="AU8">
         <f t="shared" si="3"/>
-        <v>91</v>
+        <v>128</v>
       </c>
       <c r="AV8">
         <f t="shared" si="3"/>
-        <v>91</v>
+        <v>128</v>
       </c>
       <c r="AW8">
         <f t="shared" si="3"/>
-        <v>91</v>
+        <v>128</v>
       </c>
       <c r="AX8">
         <f t="shared" si="3"/>
-        <v>91</v>
+        <v>128</v>
       </c>
       <c r="AY8">
         <f t="shared" si="3"/>
-        <v>91</v>
+        <v>128</v>
       </c>
       <c r="AZ8">
         <f t="shared" si="3"/>
-        <v>91</v>
+        <v>128</v>
       </c>
       <c r="BB8" s="44" t="str">
         <f t="shared" si="0"/>
@@ -12410,11 +12522,11 @@
       </c>
       <c r="BC8" s="44">
         <f t="shared" si="1"/>
-        <v>91</v>
+        <v>109</v>
       </c>
       <c r="BD8" s="44">
         <f t="shared" si="2"/>
-        <v>113</v>
+        <v>110</v>
       </c>
     </row>
     <row r="9" spans="1:56" ht="21.6" x14ac:dyDescent="0.4">
@@ -12471,51 +12583,51 @@
       </c>
       <c r="N9">
         <f>M9+'Drivers'' Standings'!O9</f>
-        <v>60</v>
+        <v>68</v>
       </c>
       <c r="O9">
         <f>N9+'Drivers'' Standings'!P9</f>
-        <v>60</v>
+        <v>68</v>
       </c>
       <c r="P9">
         <f>O9+'Drivers'' Standings'!Q9</f>
-        <v>60</v>
+        <v>68</v>
       </c>
       <c r="Q9">
         <f>P9+'Drivers'' Standings'!R9</f>
-        <v>60</v>
+        <v>68</v>
       </c>
       <c r="R9">
         <f>Q9+'Drivers'' Standings'!S9</f>
-        <v>60</v>
+        <v>68</v>
       </c>
       <c r="S9">
         <f>R9+'Drivers'' Standings'!T9</f>
-        <v>60</v>
+        <v>68</v>
       </c>
       <c r="T9">
         <f>S9+'Drivers'' Standings'!U9</f>
-        <v>60</v>
+        <v>68</v>
       </c>
       <c r="U9">
         <f>T9+'Drivers'' Standings'!V9</f>
-        <v>60</v>
+        <v>68</v>
       </c>
       <c r="V9">
         <f>U9+'Drivers'' Standings'!W9</f>
-        <v>60</v>
+        <v>68</v>
       </c>
       <c r="W9">
         <f>V9+'Drivers'' Standings'!X9</f>
-        <v>60</v>
+        <v>68</v>
       </c>
       <c r="X9">
         <f>W9+'Drivers'' Standings'!Y9</f>
-        <v>60</v>
+        <v>68</v>
       </c>
       <c r="Y9">
         <f>X9+'Drivers'' Standings'!Z9</f>
-        <v>60</v>
+        <v>68</v>
       </c>
       <c r="AB9" t="str">
         <f>AF2</f>
@@ -12571,51 +12683,51 @@
       </c>
       <c r="AO9">
         <f t="shared" si="3"/>
-        <v>204</v>
+        <v>219</v>
       </c>
       <c r="AP9">
         <f t="shared" si="3"/>
-        <v>204</v>
+        <v>219</v>
       </c>
       <c r="AQ9">
         <f t="shared" si="3"/>
-        <v>204</v>
+        <v>219</v>
       </c>
       <c r="AR9">
         <f t="shared" si="3"/>
-        <v>204</v>
+        <v>219</v>
       </c>
       <c r="AS9">
         <f t="shared" si="3"/>
-        <v>204</v>
+        <v>219</v>
       </c>
       <c r="AT9">
         <f t="shared" si="3"/>
-        <v>204</v>
+        <v>219</v>
       </c>
       <c r="AU9">
         <f t="shared" si="3"/>
-        <v>204</v>
+        <v>219</v>
       </c>
       <c r="AV9">
         <f t="shared" si="3"/>
-        <v>204</v>
+        <v>219</v>
       </c>
       <c r="AW9">
         <f t="shared" si="3"/>
-        <v>204</v>
+        <v>219</v>
       </c>
       <c r="AX9">
         <f t="shared" si="3"/>
-        <v>204</v>
+        <v>219</v>
       </c>
       <c r="AY9">
         <f t="shared" si="3"/>
-        <v>204</v>
+        <v>219</v>
       </c>
       <c r="AZ9">
         <f t="shared" si="3"/>
-        <v>204</v>
+        <v>219</v>
       </c>
       <c r="BB9" s="44" t="str">
         <f t="shared" si="0"/>
@@ -12623,11 +12735,11 @@
       </c>
       <c r="BC9" s="44">
         <f t="shared" si="1"/>
-        <v>60</v>
+        <v>68</v>
       </c>
       <c r="BD9" s="44">
         <f t="shared" si="2"/>
-        <v>144</v>
+        <v>151</v>
       </c>
     </row>
     <row r="10" spans="1:56" ht="21.6" x14ac:dyDescent="0.4">
@@ -12740,7 +12852,7 @@
       </c>
       <c r="BD10" s="44">
         <f t="shared" si="2"/>
-        <v>162</v>
+        <v>177</v>
       </c>
     </row>
     <row r="11" spans="1:56" ht="21.6" x14ac:dyDescent="0.4">
@@ -12853,7 +12965,7 @@
       </c>
       <c r="BD11" s="44">
         <f t="shared" si="2"/>
-        <v>185</v>
+        <v>200</v>
       </c>
     </row>
     <row r="12" spans="1:56" ht="21.6" x14ac:dyDescent="0.4">
@@ -12910,51 +13022,51 @@
       </c>
       <c r="N12">
         <f>M12+'Drivers'' Standings'!O12</f>
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="O12">
         <f>N12+'Drivers'' Standings'!P12</f>
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="P12">
         <f>O12+'Drivers'' Standings'!Q12</f>
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Q12">
         <f>P12+'Drivers'' Standings'!R12</f>
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="R12">
         <f>Q12+'Drivers'' Standings'!S12</f>
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="S12">
         <f>R12+'Drivers'' Standings'!T12</f>
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="T12">
         <f>S12+'Drivers'' Standings'!U12</f>
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="U12">
         <f>T12+'Drivers'' Standings'!V12</f>
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="V12">
         <f>U12+'Drivers'' Standings'!W12</f>
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="W12">
         <f>V12+'Drivers'' Standings'!X12</f>
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="X12">
         <f>W12+'Drivers'' Standings'!Y12</f>
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Y12">
         <f>X12+'Drivers'' Standings'!Z12</f>
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BB12" s="44" t="str">
         <f t="shared" si="0"/>
@@ -12962,11 +13074,11 @@
       </c>
       <c r="BC12" s="44">
         <f t="shared" si="1"/>
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BD12" s="44">
         <f t="shared" si="2"/>
-        <v>182</v>
+        <v>196</v>
       </c>
     </row>
     <row r="13" spans="1:56" ht="21.6" x14ac:dyDescent="0.4">
@@ -13023,51 +13135,51 @@
       </c>
       <c r="N13">
         <f>M13+'Drivers'' Standings'!O13</f>
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="O13">
         <f>N13+'Drivers'' Standings'!P13</f>
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="P13">
         <f>O13+'Drivers'' Standings'!Q13</f>
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="Q13">
         <f>P13+'Drivers'' Standings'!R13</f>
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="R13">
         <f>Q13+'Drivers'' Standings'!S13</f>
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="S13">
         <f>R13+'Drivers'' Standings'!T13</f>
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="T13">
         <f>S13+'Drivers'' Standings'!U13</f>
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="U13">
         <f>T13+'Drivers'' Standings'!V13</f>
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="V13">
         <f>U13+'Drivers'' Standings'!W13</f>
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="W13">
         <f>V13+'Drivers'' Standings'!X13</f>
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="X13">
         <f>W13+'Drivers'' Standings'!Y13</f>
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="Y13">
         <f>X13+'Drivers'' Standings'!Z13</f>
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="BB13" s="44" t="str">
         <f t="shared" si="0"/>
@@ -13075,11 +13187,11 @@
       </c>
       <c r="BC13" s="44">
         <f t="shared" si="1"/>
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="BD13" s="44">
         <f t="shared" si="2"/>
-        <v>165</v>
+        <v>176</v>
       </c>
     </row>
     <row r="14" spans="1:56" ht="21.6" x14ac:dyDescent="0.4">
@@ -13192,7 +13304,7 @@
       </c>
       <c r="BD14" s="44">
         <f t="shared" si="2"/>
-        <v>186</v>
+        <v>201</v>
       </c>
     </row>
     <row r="15" spans="1:56" ht="21.6" x14ac:dyDescent="0.4">
@@ -13305,7 +13417,7 @@
       </c>
       <c r="BD15" s="44">
         <f t="shared" si="2"/>
-        <v>201</v>
+        <v>216</v>
       </c>
     </row>
     <row r="16" spans="1:56" ht="21.6" x14ac:dyDescent="0.4">
@@ -13362,51 +13474,51 @@
       </c>
       <c r="N16">
         <f>M16+'Drivers'' Standings'!O16</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O16">
         <f>N16+'Drivers'' Standings'!P16</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P16">
         <f>O16+'Drivers'' Standings'!Q16</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q16">
         <f>P16+'Drivers'' Standings'!R16</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R16">
         <f>Q16+'Drivers'' Standings'!S16</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S16">
         <f>R16+'Drivers'' Standings'!T16</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="T16">
         <f>S16+'Drivers'' Standings'!U16</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U16">
         <f>T16+'Drivers'' Standings'!V16</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V16">
         <f>U16+'Drivers'' Standings'!W16</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W16">
         <f>V16+'Drivers'' Standings'!X16</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X16">
         <f>W16+'Drivers'' Standings'!Y16</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Y16">
         <f>X16+'Drivers'' Standings'!Z16</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BB16" s="44" t="str">
         <f t="shared" si="0"/>
@@ -13414,11 +13526,11 @@
       </c>
       <c r="BC16" s="44">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BD16" s="44">
         <f t="shared" si="2"/>
-        <v>204</v>
+        <v>217</v>
       </c>
     </row>
     <row r="17" spans="1:56" ht="21.6" x14ac:dyDescent="0.4">
@@ -13531,7 +13643,7 @@
       </c>
       <c r="BD17" s="44">
         <f t="shared" si="2"/>
-        <v>194</v>
+        <v>209</v>
       </c>
     </row>
     <row r="18" spans="1:56" ht="21.6" x14ac:dyDescent="0.4">
@@ -13644,7 +13756,7 @@
       </c>
       <c r="BD18" s="44">
         <f t="shared" si="2"/>
-        <v>199</v>
+        <v>214</v>
       </c>
     </row>
     <row r="19" spans="1:56" ht="21.6" x14ac:dyDescent="0.4">
@@ -13757,7 +13869,7 @@
       </c>
       <c r="BD19" s="44">
         <f t="shared" si="2"/>
-        <v>198</v>
+        <v>213</v>
       </c>
     </row>
     <row r="20" spans="1:56" ht="21.6" x14ac:dyDescent="0.4">
@@ -13870,7 +13982,7 @@
       </c>
       <c r="BD20" s="44">
         <f t="shared" si="2"/>
-        <v>203</v>
+        <v>218</v>
       </c>
     </row>
     <row r="21" spans="1:56" ht="21.6" x14ac:dyDescent="0.4">
@@ -13983,7 +14095,7 @@
       </c>
       <c r="BD21" s="44">
         <f t="shared" si="2"/>
-        <v>204</v>
+        <v>219</v>
       </c>
     </row>
     <row r="22" spans="1:56" ht="21.6" x14ac:dyDescent="0.4">
@@ -14096,7 +14208,7 @@
       </c>
       <c r="BD22" s="44">
         <f t="shared" si="2"/>
-        <v>204</v>
+        <v>219</v>
       </c>
     </row>
     <row r="23" spans="1:56" ht="21.6" x14ac:dyDescent="0.4">
@@ -14209,7 +14321,7 @@
       </c>
       <c r="BD23" s="44">
         <f t="shared" si="2"/>
-        <v>204</v>
+        <v>219</v>
       </c>
     </row>
   </sheetData>
@@ -14387,10 +14499,10 @@
       <c r="B11" s="18">
         <v>1</v>
       </c>
-      <c r="D11" s="48" t="s">
+      <c r="D11" s="59" t="s">
         <v>98</v>
       </c>
-      <c r="E11" s="49"/>
+      <c r="E11" s="60"/>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A12" s="18" t="s">
@@ -14401,10 +14513,10 @@
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A13" s="48" t="s">
+      <c r="A13" s="59" t="s">
         <v>97</v>
       </c>
-      <c r="B13" s="48"/>
+      <c r="B13" s="59"/>
     </row>
   </sheetData>
   <mergeCells count="2">
